--- a/mapping_file_creator/primer_lists.xlsx
+++ b/mapping_file_creator/primer_lists.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{B52CF759-285B-441E-BEA9-BDA3F1DCDF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EE5BBBC-06DD-4976-8A82-2F2CCAB915DC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="16" xr2:uid="{65C7B25E-2C2E-405F-B0A1-59E254FD8C68}"/>
+    <workbookView xWindow="-16320" yWindow="-6525" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{65C7B25E-2C2E-405F-B0A1-59E254FD8C68}"/>
   </bookViews>
   <sheets>
     <sheet name="515F_Golay" sheetId="5" r:id="rId1"/>

--- a/mapping_file_creator/primer_lists.xlsx
+++ b/mapping_file_creator/primer_lists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://joinnioz-my.sharepoint.com/personal/maartje_brouwer_nioz_nl/Documents/Documenten/GitHub/molecular_tools/mapping_file_creator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{B52CF759-285B-441E-BEA9-BDA3F1DCDF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EE5BBBC-06DD-4976-8A82-2F2CCAB915DC}"/>
+  <xr:revisionPtr revIDLastSave="629" documentId="13_ncr:1_{B52CF759-285B-441E-BEA9-BDA3F1DCDF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{448548E3-1BE5-48D7-8DC1-6ED458AA85FD}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-6525" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{65C7B25E-2C2E-405F-B0A1-59E254FD8C68}"/>
+    <workbookView xWindow="-8" yWindow="8002" windowWidth="20715" windowHeight="13155" firstSheet="14" activeTab="14" xr2:uid="{65C7B25E-2C2E-405F-B0A1-59E254FD8C68}"/>
   </bookViews>
   <sheets>
     <sheet name="515F_Golay" sheetId="5" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="M13R_Golay" sheetId="19" r:id="rId17"/>
     <sheet name="M13_Golay" sheetId="16" r:id="rId18"/>
     <sheet name="SpudR_Golay" sheetId="17" r:id="rId19"/>
+    <sheet name="GroupLinda_Golays" sheetId="24" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6740" uniqueCount="3759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7903" uniqueCount="4582">
   <si>
     <t>TTCACTGACGGG</t>
   </si>
@@ -11342,12 +11343,2481 @@
   <si>
     <t>Complete_sequence</t>
   </si>
+  <si>
+    <t>TGTAAAACGACGGCCAGT</t>
+  </si>
+  <si>
+    <t>CAGGAAACAGCTATGACC</t>
+  </si>
+  <si>
+    <t>Golay Barcode</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>HYD1_Golay01</t>
+  </si>
+  <si>
+    <t>515rcbc801</t>
+  </si>
+  <si>
+    <t>TCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>CTAATTCTCTGC</t>
+  </si>
+  <si>
+    <t>CTAATTCTCTGCTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay03</t>
+  </si>
+  <si>
+    <t>515rcbc803</t>
+  </si>
+  <si>
+    <t>ATGAGGGTCGCG</t>
+  </si>
+  <si>
+    <t>ATGAGGGTCGCGTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay05</t>
+  </si>
+  <si>
+    <t>515rcbc805</t>
+  </si>
+  <si>
+    <t>TATTCGTATTCG</t>
+  </si>
+  <si>
+    <t>TATTCGTATTCGTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay07</t>
+  </si>
+  <si>
+    <t>515rcbc807</t>
+  </si>
+  <si>
+    <t>CGGCGCATTATA</t>
+  </si>
+  <si>
+    <t>CGGCGCATTATATCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay09</t>
+  </si>
+  <si>
+    <t>515rcbc809</t>
+  </si>
+  <si>
+    <t>GTTATCGCATGG</t>
+  </si>
+  <si>
+    <t>GTTATCGCATGGTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay11</t>
+  </si>
+  <si>
+    <t>515rcbc811</t>
+  </si>
+  <si>
+    <t>TCGAAGACGTAT</t>
+  </si>
+  <si>
+    <t>TCGAAGACGTATTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay13</t>
+  </si>
+  <si>
+    <t>515rcbc813</t>
+  </si>
+  <si>
+    <t>GTGCTAATAGGT</t>
+  </si>
+  <si>
+    <t>GTGCTAATAGGTTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay15</t>
+  </si>
+  <si>
+    <t>515rcbc815</t>
+  </si>
+  <si>
+    <t>TTCGAAACTTTC</t>
+  </si>
+  <si>
+    <t>TTCGAAACTTTCTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay17</t>
+  </si>
+  <si>
+    <t>515rcbc817</t>
+  </si>
+  <si>
+    <t>CAGTCAGGCCTT</t>
+  </si>
+  <si>
+    <t>CAGTCAGGCCTTTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay19</t>
+  </si>
+  <si>
+    <t>515rcbc819</t>
+  </si>
+  <si>
+    <t>CGCTGCTTCGGT</t>
+  </si>
+  <si>
+    <t>CGCTGCTTCGGTTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay21</t>
+  </si>
+  <si>
+    <t>515rcbc821</t>
+  </si>
+  <si>
+    <t>AGCGAGAAGTGA</t>
+  </si>
+  <si>
+    <t>AGCGAGAAGTGATCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay23</t>
+  </si>
+  <si>
+    <t>515rcbc823</t>
+  </si>
+  <si>
+    <t>CATCAGTACGCC</t>
+  </si>
+  <si>
+    <t>CATCAGTACGCCTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay25</t>
+  </si>
+  <si>
+    <t>515rcbc825</t>
+  </si>
+  <si>
+    <t>TCATCGATTTAA</t>
+  </si>
+  <si>
+    <t>TCATCGATTTAATCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay27</t>
+  </si>
+  <si>
+    <t>515rcbc827</t>
+  </si>
+  <si>
+    <t>TCGTCAAACCCG</t>
+  </si>
+  <si>
+    <t>TCGTCAAACCCGTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay29</t>
+  </si>
+  <si>
+    <t>515rcbc829</t>
+  </si>
+  <si>
+    <t>ACGAAAGAGCAG</t>
+  </si>
+  <si>
+    <t>ACGAAAGAGCAGTCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD1_Golay31</t>
+  </si>
+  <si>
+    <t>515rcbc831</t>
+  </si>
+  <si>
+    <t>CGTAGTACCACA</t>
+  </si>
+  <si>
+    <t>CGTAGTACCACATCGACTGTTTACCAAAAACATAGC</t>
+  </si>
+  <si>
+    <t>HYD2_Golay02</t>
+  </si>
+  <si>
+    <t>515rcbc802</t>
+  </si>
+  <si>
+    <t>ACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>CGTGTAGTAGAT</t>
+  </si>
+  <si>
+    <t>CGTGTAGTAGATACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay04</t>
+  </si>
+  <si>
+    <t>515rcbc804</t>
+  </si>
+  <si>
+    <t>CCATCTTACCAT</t>
+  </si>
+  <si>
+    <t>CCATCTTACCATACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay06</t>
+  </si>
+  <si>
+    <t>515rcbc806</t>
+  </si>
+  <si>
+    <t>TTAAACCGCGCC</t>
+  </si>
+  <si>
+    <t>TTAAACCGCGCCACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay08</t>
+  </si>
+  <si>
+    <t>515rcbc808</t>
+  </si>
+  <si>
+    <t>ACCAGCTCAGAT</t>
+  </si>
+  <si>
+    <t>ACCAGCTCAGATACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay10</t>
+  </si>
+  <si>
+    <t>515rcbc810</t>
+  </si>
+  <si>
+    <t>TCTGAGGTTGCC</t>
+  </si>
+  <si>
+    <t>TCTGAGGTTGCCACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay12</t>
+  </si>
+  <si>
+    <t>515rcbc812</t>
+  </si>
+  <si>
+    <t>CGATGGCGCGAC</t>
+  </si>
+  <si>
+    <t>CGATGGCGCGACACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay14</t>
+  </si>
+  <si>
+    <t>515rcbc814</t>
+  </si>
+  <si>
+    <t>CGCGCTGGCCCG</t>
+  </si>
+  <si>
+    <t>CGCGCTGGCCCGACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay16</t>
+  </si>
+  <si>
+    <t>515rcbc816</t>
+  </si>
+  <si>
+    <t>AGGCGGCCCATG</t>
+  </si>
+  <si>
+    <t>AGGCGGCCCATGACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay18</t>
+  </si>
+  <si>
+    <t>515rcbc818</t>
+  </si>
+  <si>
+    <t>GTGCGCCTTCTG</t>
+  </si>
+  <si>
+    <t>GTGCGCCTTCTGACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay20</t>
+  </si>
+  <si>
+    <t>515rcbc820</t>
+  </si>
+  <si>
+    <t>CATGCCAACATG</t>
+  </si>
+  <si>
+    <t>CATGCCAACATGACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay22</t>
+  </si>
+  <si>
+    <t>515rcbc822</t>
+  </si>
+  <si>
+    <t>TTCACTGTGCGG</t>
+  </si>
+  <si>
+    <t>TTCACTGTGCGGACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay24</t>
+  </si>
+  <si>
+    <t>515rcbc824</t>
+  </si>
+  <si>
+    <t>GTGATCGAGGGC</t>
+  </si>
+  <si>
+    <t>GTGATCGAGGGCACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay26</t>
+  </si>
+  <si>
+    <t>515rcbc826</t>
+  </si>
+  <si>
+    <t>GAGGTTCTTGAC</t>
+  </si>
+  <si>
+    <t>GAGGTTCTTGACACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay28</t>
+  </si>
+  <si>
+    <t>515rcbc828</t>
+  </si>
+  <si>
+    <t>TTGTAGCCGACA</t>
+  </si>
+  <si>
+    <t>TTGTAGCCGACAACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay30</t>
+  </si>
+  <si>
+    <t>515rcbc830</t>
+  </si>
+  <si>
+    <t>TGTGGAAACTCC</t>
+  </si>
+  <si>
+    <t>TGTGGAAACTCCACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>HYD2_Golay32</t>
+  </si>
+  <si>
+    <t>515rcbc832</t>
+  </si>
+  <si>
+    <t>CTATAACACATT</t>
+  </si>
+  <si>
+    <t>CTATAACACATTACGGAATGAACTCAAATCATGTAAG</t>
+  </si>
+  <si>
+    <t>3F_Golay31_fw</t>
+  </si>
+  <si>
+    <t>GAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>CGTAGTACCACAGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay33_fw</t>
+  </si>
+  <si>
+    <t>515rcbc833</t>
+  </si>
+  <si>
+    <t>ACAGGAGGGTGT</t>
+  </si>
+  <si>
+    <t>ACAGGAGGGTGTGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay35_fw</t>
+  </si>
+  <si>
+    <t>515rcbc835</t>
+  </si>
+  <si>
+    <t>TAATATTTCGAC</t>
+  </si>
+  <si>
+    <t>TAATATTTCGACGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay37_fw</t>
+  </si>
+  <si>
+    <t>515rcbc837</t>
+  </si>
+  <si>
+    <t>GCGTCCATGAAT</t>
+  </si>
+  <si>
+    <t>GCGTCCATGAATGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay39_fw</t>
+  </si>
+  <si>
+    <t>515rcbc839</t>
+  </si>
+  <si>
+    <t>TGTCGTCCCGCC</t>
+  </si>
+  <si>
+    <t>TGTCGTCCCGCCGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay41_fw</t>
+  </si>
+  <si>
+    <t>515rcbc841</t>
+  </si>
+  <si>
+    <t>CATAGGCCATCA</t>
+  </si>
+  <si>
+    <t>CATAGGCCATCAGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay43_fw</t>
+  </si>
+  <si>
+    <t>515rcbc843</t>
+  </si>
+  <si>
+    <t>AGCAGCTATTGC</t>
+  </si>
+  <si>
+    <t>AGCAGCTATTGCGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay45_fw</t>
+  </si>
+  <si>
+    <t>515rcbc845</t>
+  </si>
+  <si>
+    <t>ACCACTTGCCAG</t>
+  </si>
+  <si>
+    <t>ACCACTTGCCAGGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay47_fw</t>
+  </si>
+  <si>
+    <t>515rcbc847</t>
+  </si>
+  <si>
+    <t>GTGACGTTAGTC</t>
+  </si>
+  <si>
+    <t>GTGACGTTAGTCGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay49_fw</t>
+  </si>
+  <si>
+    <t>515rcbc849</t>
+  </si>
+  <si>
+    <t>CAGGCTCAGAGG</t>
+  </si>
+  <si>
+    <t>CAGGCTCAGAGGGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay51_fw</t>
+  </si>
+  <si>
+    <t>515rcbc851</t>
+  </si>
+  <si>
+    <t>GAGCAACATCCT</t>
+  </si>
+  <si>
+    <t>GAGCAACATCCTGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay53_fw</t>
+  </si>
+  <si>
+    <t>515rcbc853</t>
+  </si>
+  <si>
+    <t>CGGGCCGACGAT</t>
+  </si>
+  <si>
+    <t>CGGGCCGACGATGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay55_fw</t>
+  </si>
+  <si>
+    <t>515rcbc855</t>
+  </si>
+  <si>
+    <t>ATGAACTATGAG</t>
+  </si>
+  <si>
+    <t>ATGAACTATGAGGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay57_fw</t>
+  </si>
+  <si>
+    <t>515rcbc857</t>
+  </si>
+  <si>
+    <t>ATGGCAATTCAG</t>
+  </si>
+  <si>
+    <t>ATGGCAATTCAGGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay59_fw</t>
+  </si>
+  <si>
+    <t>515rcbc859</t>
+  </si>
+  <si>
+    <t>TCCGCGCAAGTT</t>
+  </si>
+  <si>
+    <t>TCCGCGCAAGTTGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay61_fw</t>
+  </si>
+  <si>
+    <t>515rcbc861</t>
+  </si>
+  <si>
+    <t>ATCATTGATTAC</t>
+  </si>
+  <si>
+    <t>ATCATTGATTACGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay63_fw</t>
+  </si>
+  <si>
+    <t>515rcbc863</t>
+  </si>
+  <si>
+    <t>AGATCTATGCAG</t>
+  </si>
+  <si>
+    <t>AGATCTATGCAGGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay65_fw</t>
+  </si>
+  <si>
+    <t>515rcbc865</t>
+  </si>
+  <si>
+    <t>CCATATCCCGGA</t>
+  </si>
+  <si>
+    <t>CCATATCCCGGAGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay67_fw</t>
+  </si>
+  <si>
+    <t>515rcbc867</t>
+  </si>
+  <si>
+    <t>TACCAATCGGTG</t>
+  </si>
+  <si>
+    <t>TACCAATCGGTGGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay69_fw</t>
+  </si>
+  <si>
+    <t>515rcbc869</t>
+  </si>
+  <si>
+    <t>ACTCGTGATAGC</t>
+  </si>
+  <si>
+    <t>ACTCGTGATAGCGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay71_fw</t>
+  </si>
+  <si>
+    <t>515rcbc871</t>
+  </si>
+  <si>
+    <t>AGACATACCGTA</t>
+  </si>
+  <si>
+    <t>AGACATACCGTAGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay73_fw</t>
+  </si>
+  <si>
+    <t>515rcbc873</t>
+  </si>
+  <si>
+    <t>AGTGAAATACTG</t>
+  </si>
+  <si>
+    <t>AGTGAAATACTGGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay75_fw</t>
+  </si>
+  <si>
+    <t>515rcbc875</t>
+  </si>
+  <si>
+    <t>GATTTAGAGGCT</t>
+  </si>
+  <si>
+    <t>GATTTAGAGGCTGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay77_fw</t>
+  </si>
+  <si>
+    <t>515rcbc877</t>
+  </si>
+  <si>
+    <t>CGATAGGCCTTA</t>
+  </si>
+  <si>
+    <t>CGATAGGCCTTAGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay79_fw</t>
+  </si>
+  <si>
+    <t>515rcbc879</t>
+  </si>
+  <si>
+    <t>TCCGCAACCTGA</t>
+  </si>
+  <si>
+    <t>TCCGCAACCTGAGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay81_fw</t>
+  </si>
+  <si>
+    <t>515rcbc881</t>
+  </si>
+  <si>
+    <t>GTGTTCCCAGAA</t>
+  </si>
+  <si>
+    <t>GTGTTCCCAGAAGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay83_fw</t>
+  </si>
+  <si>
+    <t>515rcbc883</t>
+  </si>
+  <si>
+    <t>GCTGTGATTCGA</t>
+  </si>
+  <si>
+    <t>GCTGTGATTCGAGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay85_fw</t>
+  </si>
+  <si>
+    <t>515rcbc885</t>
+  </si>
+  <si>
+    <t>TTGGGTACACGT</t>
+  </si>
+  <si>
+    <t>TTGGGTACACGTGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay87_fw</t>
+  </si>
+  <si>
+    <t>515rcbc887</t>
+  </si>
+  <si>
+    <t>AACGCGAAATTC</t>
+  </si>
+  <si>
+    <t>AACGCGAAATTCGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay89_fw</t>
+  </si>
+  <si>
+    <t>515rcbc889</t>
+  </si>
+  <si>
+    <t>CGATCGAACACT</t>
+  </si>
+  <si>
+    <t>CGATCGAACACTGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay91_fw</t>
+  </si>
+  <si>
+    <t>515rcbc891</t>
+  </si>
+  <si>
+    <t>GCAGGGTCGAAC</t>
+  </si>
+  <si>
+    <t>GCAGGGTCGAACGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay93_fw</t>
+  </si>
+  <si>
+    <t>515rcbc893</t>
+  </si>
+  <si>
+    <t>CAGGTAATAATG</t>
+  </si>
+  <si>
+    <t>CAGGTAATAATGGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay95_fw</t>
+  </si>
+  <si>
+    <t>515rcbc895</t>
+  </si>
+  <si>
+    <t>GTCTAGTATTTC</t>
+  </si>
+  <si>
+    <t>GTCTAGTATTTCGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay97_fw</t>
+  </si>
+  <si>
+    <t>515rcbc897</t>
+  </si>
+  <si>
+    <t>CCGCTGATGTCA</t>
+  </si>
+  <si>
+    <t>CCGCTGATGTCAGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3F_Golay99_fw</t>
+  </si>
+  <si>
+    <t>515rcbc899</t>
+  </si>
+  <si>
+    <t>GGTGACTAGTTC</t>
+  </si>
+  <si>
+    <t>GGTGACTAGTTCGAAGCTCGCTGTGATTGCTG</t>
+  </si>
+  <si>
+    <t>3330R_Golay32_rv</t>
+  </si>
+  <si>
+    <t>GCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>CTATAACACATTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay34_rv</t>
+  </si>
+  <si>
+    <t>515rcbc834</t>
+  </si>
+  <si>
+    <t>GCAACCGATTGT</t>
+  </si>
+  <si>
+    <t>GCAACCGATTGTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay36_rv</t>
+  </si>
+  <si>
+    <t>515rcbc836</t>
+  </si>
+  <si>
+    <t>CGGGCGAATTGG</t>
+  </si>
+  <si>
+    <t>CGGGCGAATTGGGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay38_rv</t>
+  </si>
+  <si>
+    <t>515rcbc838</t>
+  </si>
+  <si>
+    <t>AGTTGAGGCATT</t>
+  </si>
+  <si>
+    <t>AGTTGAGGCATTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay40_rv</t>
+  </si>
+  <si>
+    <t>515rcbc840</t>
+  </si>
+  <si>
+    <t>CTCAAGTCAAAG</t>
+  </si>
+  <si>
+    <t>CTCAAGTCAAAGGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay42_rv</t>
+  </si>
+  <si>
+    <t>515rcbc842</t>
+  </si>
+  <si>
+    <t>ACGCCACTTGCC</t>
+  </si>
+  <si>
+    <t>ACGCCACTTGCCGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay44_rv</t>
+  </si>
+  <si>
+    <t>515rcbc844</t>
+  </si>
+  <si>
+    <t>CGCTTGTGTAGC</t>
+  </si>
+  <si>
+    <t>CGCTTGTGTAGCGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay46_rv</t>
+  </si>
+  <si>
+    <t>515rcbc846</t>
+  </si>
+  <si>
+    <t>CGAAATGCATGT</t>
+  </si>
+  <si>
+    <t>CGAAATGCATGTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay48_rv</t>
+  </si>
+  <si>
+    <t>515rcbc848</t>
+  </si>
+  <si>
+    <t>TCCGTCATGGGT</t>
+  </si>
+  <si>
+    <t>TCCGTCATGGGTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay50_rv</t>
+  </si>
+  <si>
+    <t>515rcbc850</t>
+  </si>
+  <si>
+    <t>CAAGCGTTGTCC</t>
+  </si>
+  <si>
+    <t>CAAGCGTTGTCCGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay52_rv</t>
+  </si>
+  <si>
+    <t>515rcbc852</t>
+  </si>
+  <si>
+    <t>AGTCGGCATCTC</t>
+  </si>
+  <si>
+    <t>AGTCGGCATCTCGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay54_rv</t>
+  </si>
+  <si>
+    <t>515rcbc854</t>
+  </si>
+  <si>
+    <t>AAGTCGACACAT</t>
+  </si>
+  <si>
+    <t>AAGTCGACACATGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay56_rv</t>
+  </si>
+  <si>
+    <t>515rcbc856</t>
+  </si>
+  <si>
+    <t>GTGTTAGATGTG</t>
+  </si>
+  <si>
+    <t>GTGTTAGATGTGGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay58_rv</t>
+  </si>
+  <si>
+    <t>515rcbc858</t>
+  </si>
+  <si>
+    <t>GTACACTGATAG</t>
+  </si>
+  <si>
+    <t>GTACACTGATAGGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay60_rv</t>
+  </si>
+  <si>
+    <t>515rcbc860</t>
+  </si>
+  <si>
+    <t>TAGGCCATGTAA</t>
+  </si>
+  <si>
+    <t>TAGGCCATGTAAGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay62_rv</t>
+  </si>
+  <si>
+    <t>515rcbc862</t>
+  </si>
+  <si>
+    <t>GTACCAGGTACT</t>
+  </si>
+  <si>
+    <t>GTACCAGGTACTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay64_rv</t>
+  </si>
+  <si>
+    <t>515rcbc864</t>
+  </si>
+  <si>
+    <t>TGTGTTACTCCT</t>
+  </si>
+  <si>
+    <t>TGTGTTACTCCTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay66_rv</t>
+  </si>
+  <si>
+    <t>515rcbc866</t>
+  </si>
+  <si>
+    <t>TTGACGACATCG</t>
+  </si>
+  <si>
+    <t>TTGACGACATCGGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay68_rv</t>
+  </si>
+  <si>
+    <t>515rcbc868</t>
+  </si>
+  <si>
+    <t>ATCTGGACGATC</t>
+  </si>
+  <si>
+    <t>ATCTGGACGATCGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay70_rv</t>
+  </si>
+  <si>
+    <t>515rcbc870</t>
+  </si>
+  <si>
+    <t>ATGTGGCGTGTT</t>
+  </si>
+  <si>
+    <t>ATGTGGCGTGTTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay72_rv</t>
+  </si>
+  <si>
+    <t>515rcbc872</t>
+  </si>
+  <si>
+    <t>ACCTCTATTCGT</t>
+  </si>
+  <si>
+    <t>ACCTCTATTCGTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay74_rv</t>
+  </si>
+  <si>
+    <t>515rcbc874</t>
+  </si>
+  <si>
+    <t>ACCTTCGCGCAC</t>
+  </si>
+  <si>
+    <t>ACCTTCGCGCACGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay76_rv</t>
+  </si>
+  <si>
+    <t>515rcbc876</t>
+  </si>
+  <si>
+    <t>AAGGCTGGGCAC</t>
+  </si>
+  <si>
+    <t>AAGGCTGGGCACGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay78_rv</t>
+  </si>
+  <si>
+    <t>515rcbc878</t>
+  </si>
+  <si>
+    <t>TAAGATGCAGTC</t>
+  </si>
+  <si>
+    <t>TAAGATGCAGTCGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay80_rv</t>
+  </si>
+  <si>
+    <t>515rcbc880</t>
+  </si>
+  <si>
+    <t>AGCCGACTCTGT</t>
+  </si>
+  <si>
+    <t>AGCCGACTCTGTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay82_rv</t>
+  </si>
+  <si>
+    <t>515rcbc882</t>
+  </si>
+  <si>
+    <t>CTCGAGCGTACT</t>
+  </si>
+  <si>
+    <t>CTCGAGCGTACTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay84_rv</t>
+  </si>
+  <si>
+    <t>515rcbc884</t>
+  </si>
+  <si>
+    <t>CTGCCCTCGATG</t>
+  </si>
+  <si>
+    <t>CTGCCCTCGATGGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay86_rv</t>
+  </si>
+  <si>
+    <t>515rcbc886</t>
+  </si>
+  <si>
+    <t>GATATCGATGAA</t>
+  </si>
+  <si>
+    <t>GATATCGATGAAGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay88_rv</t>
+  </si>
+  <si>
+    <t>515rcbc888</t>
+  </si>
+  <si>
+    <t>GTGAGCACGCAG</t>
+  </si>
+  <si>
+    <t>GTGAGCACGCAGGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay90_rv</t>
+  </si>
+  <si>
+    <t>515rcbc890</t>
+  </si>
+  <si>
+    <t>TTCGCTAACCTT</t>
+  </si>
+  <si>
+    <t>TTCGCTAACCTTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay92_rv</t>
+  </si>
+  <si>
+    <t>515rcbc892</t>
+  </si>
+  <si>
+    <t>TAGAGGCGTAGG</t>
+  </si>
+  <si>
+    <t>TAGAGGCGTAGGGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay94_rv</t>
+  </si>
+  <si>
+    <t>515rcbc894</t>
+  </si>
+  <si>
+    <t>GCCGAACGCCGA</t>
+  </si>
+  <si>
+    <t>GCCGAACGCCGAGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay96_rv</t>
+  </si>
+  <si>
+    <t>515rcbc896</t>
+  </si>
+  <si>
+    <t>AAGCATTGAGAT</t>
+  </si>
+  <si>
+    <t>AAGCATTGAGATGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay98_rv</t>
+  </si>
+  <si>
+    <t>515rcbc898</t>
+  </si>
+  <si>
+    <t>ACCCTCAGCCCA</t>
+  </si>
+  <si>
+    <t>ACCCTCAGCCCAGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>3330R_Golay100_rv</t>
+  </si>
+  <si>
+    <t>515rcbc900</t>
+  </si>
+  <si>
+    <t>CCGTCAAGATGT</t>
+  </si>
+  <si>
+    <t>CCGTCAAGATGTGCGAAAGAAGCTATCCTCC</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0001</t>
+  </si>
+  <si>
+    <t>515rcbc901</t>
+  </si>
+  <si>
+    <t>AGCTGCACCTAA</t>
+  </si>
+  <si>
+    <t>GTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>AGCTGCACCTAAGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0002</t>
+  </si>
+  <si>
+    <t>515rcbc902</t>
+  </si>
+  <si>
+    <t>GGAGTGCCCGAA</t>
+  </si>
+  <si>
+    <t>GGAGTGCCCGAAGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0003</t>
+  </si>
+  <si>
+    <t>515rcbc903</t>
+  </si>
+  <si>
+    <t>CATGACGCCTCC</t>
+  </si>
+  <si>
+    <t>CATGACGCCTCCGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0004</t>
+  </si>
+  <si>
+    <t>515rcbc904</t>
+  </si>
+  <si>
+    <t>GTATTATGACTT</t>
+  </si>
+  <si>
+    <t>GTATTATGACTTGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0005</t>
+  </si>
+  <si>
+    <t>515rcbc905</t>
+  </si>
+  <si>
+    <t>CATAATCTTGCT</t>
+  </si>
+  <si>
+    <t>CATAATCTTGCTGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0006</t>
+  </si>
+  <si>
+    <t>515rcbc906</t>
+  </si>
+  <si>
+    <t>TGCGTGGGTGGA</t>
+  </si>
+  <si>
+    <t>TGCGTGGGTGGAGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0007</t>
+  </si>
+  <si>
+    <t>515rcbc907</t>
+  </si>
+  <si>
+    <t>ACTATATTAGCT</t>
+  </si>
+  <si>
+    <t>ACTATATTAGCTGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0008</t>
+  </si>
+  <si>
+    <t>515rcbc908</t>
+  </si>
+  <si>
+    <t>TTCTGGTCTTGT</t>
+  </si>
+  <si>
+    <t>TTCTGGTCTTGTGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0009</t>
+  </si>
+  <si>
+    <t>515rcbc909</t>
+  </si>
+  <si>
+    <t>TCCAGGGCTATA</t>
+  </si>
+  <si>
+    <t>TCCAGGGCTATAGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0010</t>
+  </si>
+  <si>
+    <t>515rcbc910</t>
+  </si>
+  <si>
+    <t>GACTATAATGGC</t>
+  </si>
+  <si>
+    <t>GACTATAATGGCGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0011</t>
+  </si>
+  <si>
+    <t>515rcbc911</t>
+  </si>
+  <si>
+    <t>ATCACCAGGTGT</t>
+  </si>
+  <si>
+    <t>ATCACCAGGTGTGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0012</t>
+  </si>
+  <si>
+    <t>515rcbc912</t>
+  </si>
+  <si>
+    <t>AATTGAATTTAC</t>
+  </si>
+  <si>
+    <t>AATTGAATTTACGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0013</t>
+  </si>
+  <si>
+    <t>515rcbc913</t>
+  </si>
+  <si>
+    <t>AGGAAAGCCAGA</t>
+  </si>
+  <si>
+    <t>AGGAAAGCCAGAGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0014</t>
+  </si>
+  <si>
+    <t>515rcbc914</t>
+  </si>
+  <si>
+    <t>ATGGCTGTCAGT</t>
+  </si>
+  <si>
+    <t>ATGGCTGTCAGTGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0015</t>
+  </si>
+  <si>
+    <t>515rcbc915</t>
+  </si>
+  <si>
+    <t>GAGGGTTGTCGG</t>
+  </si>
+  <si>
+    <t>GAGGGTTGTCGGGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0016</t>
+  </si>
+  <si>
+    <t>515rcbc916</t>
+  </si>
+  <si>
+    <t>CCACGTACGTAA</t>
+  </si>
+  <si>
+    <t>CCACGTACGTAAGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0017</t>
+  </si>
+  <si>
+    <t>515rcbc917</t>
+  </si>
+  <si>
+    <t>AGTAAGTCGATA</t>
+  </si>
+  <si>
+    <t>AGTAAGTCGATAGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0018</t>
+  </si>
+  <si>
+    <t>515rcbc918</t>
+  </si>
+  <si>
+    <t>TTGGGCCACATA</t>
+  </si>
+  <si>
+    <t>TTGGGCCACATAGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0019</t>
+  </si>
+  <si>
+    <t>515rcbc919</t>
+  </si>
+  <si>
+    <t>TCTATCTGGCTT</t>
+  </si>
+  <si>
+    <t>TCTATCTGGCTTGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0020</t>
+  </si>
+  <si>
+    <t>515rcbc920</t>
+  </si>
+  <si>
+    <t>ATACCTAAATAT</t>
+  </si>
+  <si>
+    <t>ATACCTAAATATGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0021</t>
+  </si>
+  <si>
+    <t>515rcbc921</t>
+  </si>
+  <si>
+    <t>GCCTGCAGTACT</t>
+  </si>
+  <si>
+    <t>GCCTGCAGTACTGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0022</t>
+  </si>
+  <si>
+    <t>515rcbc922</t>
+  </si>
+  <si>
+    <t>ATGGTTCACCCG</t>
+  </si>
+  <si>
+    <t>ATGGTTCACCCGGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0023</t>
+  </si>
+  <si>
+    <t>515rcbc923</t>
+  </si>
+  <si>
+    <t>CCGTGGACCAGG</t>
+  </si>
+  <si>
+    <t>CCGTGGACCAGGGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0024</t>
+  </si>
+  <si>
+    <t>515rcbc924</t>
+  </si>
+  <si>
+    <t>GTCCCTATTATC</t>
+  </si>
+  <si>
+    <t>GTCCCTATTATCGTGTTTCAAGCAGGCAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0001</t>
+  </si>
+  <si>
+    <t>GTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>AGCTGCACCTAAGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0002</t>
+  </si>
+  <si>
+    <t>GGAGTGCCCGAAGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0003</t>
+  </si>
+  <si>
+    <t>CATGACGCCTCCGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0004</t>
+  </si>
+  <si>
+    <t>GTATTATGACTTGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0005</t>
+  </si>
+  <si>
+    <t>CATAATCTTGCTGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0006</t>
+  </si>
+  <si>
+    <t>TGCGTGGGTGGAGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0007</t>
+  </si>
+  <si>
+    <t>ACTATATTAGCTGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0008</t>
+  </si>
+  <si>
+    <t>TTCTGGTCTTGTGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0009</t>
+  </si>
+  <si>
+    <t>TCCAGGGCTATAGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0010</t>
+  </si>
+  <si>
+    <t>GACTATAATGGCGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0011</t>
+  </si>
+  <si>
+    <t>ATCACCAGGTGTGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0012</t>
+  </si>
+  <si>
+    <t>AATTGAATTTACGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0013</t>
+  </si>
+  <si>
+    <t>AGGAAAGCCAGAGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0014</t>
+  </si>
+  <si>
+    <t>ATGGCTGTCAGTGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0015</t>
+  </si>
+  <si>
+    <t>GAGGGTTGTCGGGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0016</t>
+  </si>
+  <si>
+    <t>CCACGTACGTAAGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0017</t>
+  </si>
+  <si>
+    <t>AGTAAGTCGATAGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0018</t>
+  </si>
+  <si>
+    <t>TTGGGCCACATAGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0019</t>
+  </si>
+  <si>
+    <t>TCTATCTGGCTTGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0020</t>
+  </si>
+  <si>
+    <t>ATACCTAAATATGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0021</t>
+  </si>
+  <si>
+    <t>GCCTGCAGTACTGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0022</t>
+  </si>
+  <si>
+    <t>ATGGTTCACCCGGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0023</t>
+  </si>
+  <si>
+    <t>CCGTGGACCAGGGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0024</t>
+  </si>
+  <si>
+    <t>GTCCCTATTATCGTGTTTCAAGCAGGCCGTCG</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0001</t>
+  </si>
+  <si>
+    <t>515rcbc925</t>
+  </si>
+  <si>
+    <t>GCGACGCGGCAT</t>
+  </si>
+  <si>
+    <t>TCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>GCGACGCGGCATTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0002</t>
+  </si>
+  <si>
+    <t>515rcbc926</t>
+  </si>
+  <si>
+    <t>TGCGGTTGACTC</t>
+  </si>
+  <si>
+    <t>TGCGGTTGACTCTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0003</t>
+  </si>
+  <si>
+    <t>515rcbc927</t>
+  </si>
+  <si>
+    <t>CCAGGTTAATGC</t>
+  </si>
+  <si>
+    <t>CCAGGTTAATGCTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0004</t>
+  </si>
+  <si>
+    <t>515rcbc928</t>
+  </si>
+  <si>
+    <t>CGACGAGATTAT</t>
+  </si>
+  <si>
+    <t>CGACGAGATTATTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0005</t>
+  </si>
+  <si>
+    <t>515rcbc929</t>
+  </si>
+  <si>
+    <t>GCTACAAGCCCT</t>
+  </si>
+  <si>
+    <t>GCTACAAGCCCTTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0006</t>
+  </si>
+  <si>
+    <t>515rcbc930</t>
+  </si>
+  <si>
+    <t>GCACATAGTCGT</t>
+  </si>
+  <si>
+    <t>GCACATAGTCGTTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0007</t>
+  </si>
+  <si>
+    <t>515rcbc931</t>
+  </si>
+  <si>
+    <t>AGCCACCCGGGA</t>
+  </si>
+  <si>
+    <t>AGCCACCCGGGATCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0008</t>
+  </si>
+  <si>
+    <t>515rcbc932</t>
+  </si>
+  <si>
+    <t>ATGTCTTCAACT</t>
+  </si>
+  <si>
+    <t>ATGTCTTCAACTTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0009</t>
+  </si>
+  <si>
+    <t>515rcbc933</t>
+  </si>
+  <si>
+    <t>ACGCACATACAA</t>
+  </si>
+  <si>
+    <t>ACGCACATACAATCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0010</t>
+  </si>
+  <si>
+    <t>515rcbc934</t>
+  </si>
+  <si>
+    <t>ATGTCCGACCAA</t>
+  </si>
+  <si>
+    <t>ATGTCCGACCAATCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0011</t>
+  </si>
+  <si>
+    <t>515rcbc935</t>
+  </si>
+  <si>
+    <t>ATTTCGACCCGG</t>
+  </si>
+  <si>
+    <t>ATTTCGACCCGGTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0012</t>
+  </si>
+  <si>
+    <t>515rcbc936</t>
+  </si>
+  <si>
+    <t>GGAGTTGAGGTG</t>
+  </si>
+  <si>
+    <t>GGAGTTGAGGTGTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0013</t>
+  </si>
+  <si>
+    <t>515rcbc937</t>
+  </si>
+  <si>
+    <t>GCGCAATAGTAT</t>
+  </si>
+  <si>
+    <t>GCGCAATAGTATTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0014</t>
+  </si>
+  <si>
+    <t>515rcbc938</t>
+  </si>
+  <si>
+    <t>CACATATTGGGC</t>
+  </si>
+  <si>
+    <t>CACATATTGGGCTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0015</t>
+  </si>
+  <si>
+    <t>515rcbc939</t>
+  </si>
+  <si>
+    <t>CATGTTGGAACA</t>
+  </si>
+  <si>
+    <t>CATGTTGGAACATCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0016</t>
+  </si>
+  <si>
+    <t>515rcbc940</t>
+  </si>
+  <si>
+    <t>ACCCGACGGGAC</t>
+  </si>
+  <si>
+    <t>ACCCGACGGGACTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0017</t>
+  </si>
+  <si>
+    <t>515rcbc941</t>
+  </si>
+  <si>
+    <t>AGGTCATCTTGG</t>
+  </si>
+  <si>
+    <t>AGGTCATCTTGGTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0018</t>
+  </si>
+  <si>
+    <t>515rcbc942</t>
+  </si>
+  <si>
+    <t>CTCTCGGCGTAA</t>
+  </si>
+  <si>
+    <t>CTCTCGGCGTAATCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0019</t>
+  </si>
+  <si>
+    <t>515rcbc943</t>
+  </si>
+  <si>
+    <t>CGAGATAGTTTG</t>
+  </si>
+  <si>
+    <t>CGAGATAGTTTGTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0020</t>
+  </si>
+  <si>
+    <t>515rcbc944</t>
+  </si>
+  <si>
+    <t>CTGCAAGCCTGT</t>
+  </si>
+  <si>
+    <t>CTGCAAGCCTGTTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0021</t>
+  </si>
+  <si>
+    <t>515rcbc945</t>
+  </si>
+  <si>
+    <t>GTTCAACAGCTG</t>
+  </si>
+  <si>
+    <t>GTTCAACAGCTGTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0022</t>
+  </si>
+  <si>
+    <t>515rcbc946</t>
+  </si>
+  <si>
+    <t>CGTTTCAAGGAC</t>
+  </si>
+  <si>
+    <t>CGTTTCAAGGACTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0023</t>
+  </si>
+  <si>
+    <t>515rcbc947</t>
+  </si>
+  <si>
+    <t>GCGAGCGAAGTA</t>
+  </si>
+  <si>
+    <t>GCGAGCGAAGTATCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0024</t>
+  </si>
+  <si>
+    <t>515rcbc948</t>
+  </si>
+  <si>
+    <t>ATCTCTGGCGCC</t>
+  </si>
+  <si>
+    <t>ATCTCTGGCGCCTCAGACTCCTTGGTCCGTGTTTCT</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0025</t>
+  </si>
+  <si>
+    <t>515rcbc949</t>
+  </si>
+  <si>
+    <t>AGACGACGTGGA</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0026</t>
+  </si>
+  <si>
+    <t>515rcbc950</t>
+  </si>
+  <si>
+    <t>ACTTCATCGTAT</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0027</t>
+  </si>
+  <si>
+    <t>515rcbc951</t>
+  </si>
+  <si>
+    <t>TGTGATCTTTAC</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0028</t>
+  </si>
+  <si>
+    <t>515rcbc952</t>
+  </si>
+  <si>
+    <t>TCCTCCGGTTGG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0029</t>
+  </si>
+  <si>
+    <t>515rcbc953</t>
+  </si>
+  <si>
+    <t>AACTTCACTTCC</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0030</t>
+  </si>
+  <si>
+    <t>515rcbc954</t>
+  </si>
+  <si>
+    <t>CGACCGGTGAAG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0031</t>
+  </si>
+  <si>
+    <t>515rcbc955</t>
+  </si>
+  <si>
+    <t>CCTCTCGGGTTG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0032</t>
+  </si>
+  <si>
+    <t>515rcbc956</t>
+  </si>
+  <si>
+    <t>GATGGCGGACTG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0033</t>
+  </si>
+  <si>
+    <t>515rcbc957</t>
+  </si>
+  <si>
+    <t>ATCTTGGAGTCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0034</t>
+  </si>
+  <si>
+    <t>515rcbc958</t>
+  </si>
+  <si>
+    <t>TGCCCTCCGTAG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0035</t>
+  </si>
+  <si>
+    <t>515rcbc959</t>
+  </si>
+  <si>
+    <t>GTTGTGGGCGCG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0036</t>
+  </si>
+  <si>
+    <t>515rcbc345</t>
+  </si>
+  <si>
+    <t>ACCACCGTAACC</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0037</t>
+  </si>
+  <si>
+    <t>515rcbc346</t>
+  </si>
+  <si>
+    <t>AGGAAGTAACTT</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0038</t>
+  </si>
+  <si>
+    <t>515rcbc347</t>
+  </si>
+  <si>
+    <t>CGTTCGCTAGCC</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0039</t>
+  </si>
+  <si>
+    <t>515rcbc348</t>
+  </si>
+  <si>
+    <t>CTCACCTAGGAA</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0040</t>
+  </si>
+  <si>
+    <t>515rcbc349</t>
+  </si>
+  <si>
+    <t>AGATGCAATGAT</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0041</t>
+  </si>
+  <si>
+    <t>515rcbc350</t>
+  </si>
+  <si>
+    <t>GCATTCGGCGTT</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0042</t>
+  </si>
+  <si>
+    <t>515rcbc351</t>
+  </si>
+  <si>
+    <t>TCTACATACATA</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0043</t>
+  </si>
+  <si>
+    <t>515rcbc352</t>
+  </si>
+  <si>
+    <t>GAGTCTTGGTAA</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0044</t>
+  </si>
+  <si>
+    <t>515rcbc353</t>
+  </si>
+  <si>
+    <t>CAGTCTAGTACG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0045</t>
+  </si>
+  <si>
+    <t>515rcbc354</t>
+  </si>
+  <si>
+    <t>GTTCGAGTGAAT</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0046</t>
+  </si>
+  <si>
+    <t>515rcbc355</t>
+  </si>
+  <si>
+    <t>AGTCCGAGTTGT</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0047</t>
+  </si>
+  <si>
+    <t>515rcbc356</t>
+  </si>
+  <si>
+    <t>CGTGAGGACCAG</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_1_0048</t>
+  </si>
+  <si>
+    <t>515rcbc357</t>
+  </si>
+  <si>
+    <t>CGGTTGGCGGGT</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0025</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0026</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0027</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0028</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0029</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0030</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0031</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0032</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0033</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0034</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0035</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0036</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0037</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0038</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0039</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0040</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0041</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0042</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0043</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0044</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0045</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0046</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0047</t>
+  </si>
+  <si>
+    <t>Iso_SSU_264F_2_0048</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0025</t>
+  </si>
+  <si>
+    <t>515rcbc358</t>
+  </si>
+  <si>
+    <t>CGATTCCTTAAT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0026</t>
+  </si>
+  <si>
+    <t>515rcbc359</t>
+  </si>
+  <si>
+    <t>TGCCTGCTCGAC</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0027</t>
+  </si>
+  <si>
+    <t>515rcbc360</t>
+  </si>
+  <si>
+    <t>TACTGTACTGTT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0028</t>
+  </si>
+  <si>
+    <t>515rcbc361</t>
+  </si>
+  <si>
+    <t>TCTCGCACTGGA</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0029</t>
+  </si>
+  <si>
+    <t>515rcbc362</t>
+  </si>
+  <si>
+    <t>ACCAGTGACTCA</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0030</t>
+  </si>
+  <si>
+    <t>515rcbc363</t>
+  </si>
+  <si>
+    <t>TGGCGCACGGAC</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0031</t>
+  </si>
+  <si>
+    <t>515rcbc364</t>
+  </si>
+  <si>
+    <t>CATTTACATCAC</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0032</t>
+  </si>
+  <si>
+    <t>515rcbc365</t>
+  </si>
+  <si>
+    <t>GTGGGACTGCGC</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0033</t>
+  </si>
+  <si>
+    <t>515rcbc366</t>
+  </si>
+  <si>
+    <t>CGGCCTAAGTTC</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0034</t>
+  </si>
+  <si>
+    <t>515rcbc367</t>
+  </si>
+  <si>
+    <t>GCTGAGCCTTTG</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0035</t>
+  </si>
+  <si>
+    <t>515rcbc368</t>
+  </si>
+  <si>
+    <t>AGAGACGCGTAG</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0036</t>
+  </si>
+  <si>
+    <t>515rcbc369</t>
+  </si>
+  <si>
+    <t>CCACCGGGCCGA</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0037</t>
+  </si>
+  <si>
+    <t>515rcbc370</t>
+  </si>
+  <si>
+    <t>AATCCGGTCACC</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0038</t>
+  </si>
+  <si>
+    <t>515rcbc371</t>
+  </si>
+  <si>
+    <t>TCTTACCCATAA</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0039</t>
+  </si>
+  <si>
+    <t>515rcbc372</t>
+  </si>
+  <si>
+    <t>CTAGAGCTCCCA</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0040</t>
+  </si>
+  <si>
+    <t>515rcbc373</t>
+  </si>
+  <si>
+    <t>GGTCTTAGCACC</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0041</t>
+  </si>
+  <si>
+    <t>515rcbc374</t>
+  </si>
+  <si>
+    <t>GCCTACTCTCGG</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0042</t>
+  </si>
+  <si>
+    <t>515rcbc375</t>
+  </si>
+  <si>
+    <t>ACTGCCCGATAC</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0043</t>
+  </si>
+  <si>
+    <t>515rcbc376</t>
+  </si>
+  <si>
+    <t>TTCTTAACGCCT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0044</t>
+  </si>
+  <si>
+    <t>515rcbc377</t>
+  </si>
+  <si>
+    <t>CTCCCGAGCTCC</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0045</t>
+  </si>
+  <si>
+    <t>515rcbc378</t>
+  </si>
+  <si>
+    <t>TAGACTTCAGAG</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0046</t>
+  </si>
+  <si>
+    <t>515rcbc379</t>
+  </si>
+  <si>
+    <t>ACTTAGACTCTT</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0047</t>
+  </si>
+  <si>
+    <t>515rcbc380</t>
+  </si>
+  <si>
+    <t>GGACCTGGATGG</t>
+  </si>
+  <si>
+    <t>LSU_Hapto20R_bis_0048</t>
+  </si>
+  <si>
+    <t>515rcbc381</t>
+  </si>
+  <si>
+    <t>TATGTGCCGGCT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11409,6 +13879,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -11444,7 +13922,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -11461,6 +13939,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Heading 1 2" xfId="2" xr:uid="{6C27F8A0-D678-488A-9148-9F45F06275E9}"/>
@@ -20430,7 +22912,7 @@
   <cols>
     <col min="1" max="1" width="26.85546875" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="63.140625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20456,7 +22938,7 @@
         <v>3728</v>
       </c>
       <c r="C2" t="s">
-        <v>3170</v>
+        <v>3759</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>3736</v>
@@ -20470,7 +22952,7 @@
         <v>3726</v>
       </c>
       <c r="C3" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>3745</v>
@@ -20484,7 +22966,7 @@
         <v>3724</v>
       </c>
       <c r="C4" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>3746</v>
@@ -20497,8 +22979,8 @@
       <c r="B5" s="11" t="s">
         <v>3722</v>
       </c>
-      <c r="C5" t="s">
-        <v>3170</v>
+      <c r="C5" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>3737</v>
@@ -20512,7 +22994,7 @@
         <v>3720</v>
       </c>
       <c r="C6" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>3747</v>
@@ -20528,8 +23010,8 @@
       <c r="B8" s="11" t="s">
         <v>3718</v>
       </c>
-      <c r="C8" t="s">
-        <v>3170</v>
+      <c r="C8" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>3738</v>
@@ -20542,8 +23024,8 @@
       <c r="B9" s="11" t="s">
         <v>3716</v>
       </c>
-      <c r="C9" t="s">
-        <v>3170</v>
+      <c r="C9" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>3739</v>
@@ -20557,7 +23039,7 @@
         <v>3714</v>
       </c>
       <c r="C10" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>3748</v>
@@ -20573,8 +23055,8 @@
       <c r="B12" s="11" t="s">
         <v>3712</v>
       </c>
-      <c r="C12" t="s">
-        <v>3170</v>
+      <c r="C12" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>3740</v>
@@ -20588,7 +23070,7 @@
         <v>3710</v>
       </c>
       <c r="C13" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>3749</v>
@@ -20601,8 +23083,8 @@
       <c r="B14" s="11" t="s">
         <v>3731</v>
       </c>
-      <c r="C14" t="s">
-        <v>3170</v>
+      <c r="C14" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>3741</v>
@@ -20616,7 +23098,7 @@
         <v>3707</v>
       </c>
       <c r="C15" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>3750</v>
@@ -20630,7 +23112,7 @@
         <v>3705</v>
       </c>
       <c r="C16" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>3751</v>
@@ -20646,8 +23128,8 @@
       <c r="B18" s="11" t="s">
         <v>3732</v>
       </c>
-      <c r="C18" t="s">
-        <v>3170</v>
+      <c r="C18" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>3742</v>
@@ -20661,7 +23143,7 @@
         <v>3702</v>
       </c>
       <c r="C19" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>3752</v>
@@ -20674,8 +23156,8 @@
       <c r="B20" s="11" t="s">
         <v>3700</v>
       </c>
-      <c r="C20" t="s">
-        <v>3170</v>
+      <c r="C20" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>3743</v>
@@ -20689,7 +23171,7 @@
         <v>3733</v>
       </c>
       <c r="C21" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>3753</v>
@@ -20702,8 +23184,8 @@
       <c r="B22" s="11" t="s">
         <v>3697</v>
       </c>
-      <c r="C22" t="s">
-        <v>3170</v>
+      <c r="C22" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>3734</v>
@@ -20717,7 +23199,7 @@
         <v>3695</v>
       </c>
       <c r="C23" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>3735</v>
@@ -20730,8 +23212,8 @@
       <c r="B24" s="11" t="s">
         <v>3693</v>
       </c>
-      <c r="C24" t="s">
-        <v>3170</v>
+      <c r="C24" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>3744</v>
@@ -20745,7 +23227,7 @@
         <v>3691</v>
       </c>
       <c r="C25" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>3754</v>
@@ -20758,8 +23240,8 @@
       <c r="B26" s="11" t="s">
         <v>3697</v>
       </c>
-      <c r="C26" t="s">
-        <v>3170</v>
+      <c r="C26" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>3734</v>
@@ -20773,7 +23255,7 @@
         <v>3695</v>
       </c>
       <c r="C27" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>3735</v>
@@ -20786,8 +23268,8 @@
       <c r="B28" s="11" t="s">
         <v>3693</v>
       </c>
-      <c r="C28" t="s">
-        <v>3170</v>
+      <c r="C28" s="12" t="s">
+        <v>3759</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>3744</v>
@@ -20801,7 +23283,7 @@
         <v>3691</v>
       </c>
       <c r="C29" t="s">
-        <v>3158</v>
+        <v>3760</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>3754</v>
@@ -27429,6 +29911,4294 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89ED78EB-1641-4039-B8A1-EB87053209CC}">
+  <dimension ref="A1:E247"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="13" customFormat="1">
+      <c r="A1" s="13" t="s">
+        <v>3730</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>2241</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>3730</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3761</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>3763</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3764</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3766</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3767</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>3768</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3769</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3770</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>3772</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3773</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3774</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>3776</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3777</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3778</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3779</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>3780</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3781</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3782</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>3784</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3785</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3786</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>3788</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3789</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3790</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3791</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3793</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3794</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3795</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>3796</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3797</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3798</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>3800</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3801</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3802</v>
+      </c>
+      <c r="E11" t="s">
+        <v>3803</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>3804</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3805</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3806</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3807</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>3808</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3809</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3810</v>
+      </c>
+      <c r="E13" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>3812</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3813</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D14" t="s">
+        <v>3814</v>
+      </c>
+      <c r="E14" t="s">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>3816</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3817</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D15" t="s">
+        <v>3818</v>
+      </c>
+      <c r="E15" t="s">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>3820</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3821</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D16" t="s">
+        <v>3822</v>
+      </c>
+      <c r="E16" t="s">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>3824</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3825</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D17" t="s">
+        <v>3826</v>
+      </c>
+      <c r="E17" t="s">
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>3828</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3829</v>
+      </c>
+      <c r="C18" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D18" t="s">
+        <v>3831</v>
+      </c>
+      <c r="E18" t="s">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>3833</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3834</v>
+      </c>
+      <c r="C19" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D19" t="s">
+        <v>3835</v>
+      </c>
+      <c r="E19" t="s">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>3837</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3838</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D20" t="s">
+        <v>3839</v>
+      </c>
+      <c r="E20" t="s">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>3841</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3842</v>
+      </c>
+      <c r="C21" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D21" t="s">
+        <v>3843</v>
+      </c>
+      <c r="E21" t="s">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>3845</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3846</v>
+      </c>
+      <c r="C22" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D22" t="s">
+        <v>3847</v>
+      </c>
+      <c r="E22" t="s">
+        <v>3848</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>3849</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3850</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D23" t="s">
+        <v>3851</v>
+      </c>
+      <c r="E23" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>3853</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3854</v>
+      </c>
+      <c r="C24" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D24" t="s">
+        <v>3855</v>
+      </c>
+      <c r="E24" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>3857</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3858</v>
+      </c>
+      <c r="C25" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D25" t="s">
+        <v>3859</v>
+      </c>
+      <c r="E25" t="s">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>3861</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3862</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D26" t="s">
+        <v>3863</v>
+      </c>
+      <c r="E26" t="s">
+        <v>3864</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>3865</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3866</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D27" t="s">
+        <v>3867</v>
+      </c>
+      <c r="E27" t="s">
+        <v>3868</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>3869</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3870</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D28" t="s">
+        <v>3871</v>
+      </c>
+      <c r="E28" t="s">
+        <v>3872</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>3873</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3874</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D29" t="s">
+        <v>3875</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3876</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>3877</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3878</v>
+      </c>
+      <c r="C30" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D30" t="s">
+        <v>3879</v>
+      </c>
+      <c r="E30" t="s">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>3881</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3882</v>
+      </c>
+      <c r="C31" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D31" t="s">
+        <v>3883</v>
+      </c>
+      <c r="E31" t="s">
+        <v>3884</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>3885</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3886</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D32" t="s">
+        <v>3887</v>
+      </c>
+      <c r="E32" t="s">
+        <v>3888</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>3889</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3890</v>
+      </c>
+      <c r="C33" t="s">
+        <v>3830</v>
+      </c>
+      <c r="D33" t="s">
+        <v>3891</v>
+      </c>
+      <c r="E33" t="s">
+        <v>3892</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>3893</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3825</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D34" t="s">
+        <v>3826</v>
+      </c>
+      <c r="E34" t="s">
+        <v>3895</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>3896</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3897</v>
+      </c>
+      <c r="C35" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D35" t="s">
+        <v>3898</v>
+      </c>
+      <c r="E35" t="s">
+        <v>3899</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>3900</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3901</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D36" t="s">
+        <v>3902</v>
+      </c>
+      <c r="E36" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>3904</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3905</v>
+      </c>
+      <c r="C37" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D37" t="s">
+        <v>3906</v>
+      </c>
+      <c r="E37" t="s">
+        <v>3907</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>3908</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C38" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D38" t="s">
+        <v>3910</v>
+      </c>
+      <c r="E38" t="s">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>3912</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3913</v>
+      </c>
+      <c r="C39" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D39" t="s">
+        <v>3914</v>
+      </c>
+      <c r="E39" t="s">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>3916</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3917</v>
+      </c>
+      <c r="C40" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D40" t="s">
+        <v>3918</v>
+      </c>
+      <c r="E40" t="s">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>3920</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3921</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D41" t="s">
+        <v>3922</v>
+      </c>
+      <c r="E41" t="s">
+        <v>3923</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>3924</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3925</v>
+      </c>
+      <c r="C42" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D42" t="s">
+        <v>3926</v>
+      </c>
+      <c r="E42" t="s">
+        <v>3927</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>3928</v>
+      </c>
+      <c r="B43" t="s">
+        <v>3929</v>
+      </c>
+      <c r="C43" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D43" t="s">
+        <v>3930</v>
+      </c>
+      <c r="E43" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>3932</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3933</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D44" t="s">
+        <v>3934</v>
+      </c>
+      <c r="E44" t="s">
+        <v>3935</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>3936</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3937</v>
+      </c>
+      <c r="C45" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D45" t="s">
+        <v>3938</v>
+      </c>
+      <c r="E45" t="s">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>3940</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3941</v>
+      </c>
+      <c r="C46" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D46" t="s">
+        <v>3942</v>
+      </c>
+      <c r="E46" t="s">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>3944</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3945</v>
+      </c>
+      <c r="C47" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D47" t="s">
+        <v>3946</v>
+      </c>
+      <c r="E47" t="s">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>3948</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3949</v>
+      </c>
+      <c r="C48" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D48" t="s">
+        <v>3950</v>
+      </c>
+      <c r="E48" t="s">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>3952</v>
+      </c>
+      <c r="B49" t="s">
+        <v>3953</v>
+      </c>
+      <c r="C49" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D49" t="s">
+        <v>3954</v>
+      </c>
+      <c r="E49" t="s">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>3956</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3957</v>
+      </c>
+      <c r="C50" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D50" t="s">
+        <v>3958</v>
+      </c>
+      <c r="E50" t="s">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>3960</v>
+      </c>
+      <c r="B51" t="s">
+        <v>3961</v>
+      </c>
+      <c r="C51" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D51" t="s">
+        <v>3962</v>
+      </c>
+      <c r="E51" t="s">
+        <v>3963</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>3964</v>
+      </c>
+      <c r="B52" t="s">
+        <v>3965</v>
+      </c>
+      <c r="C52" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D52" t="s">
+        <v>3966</v>
+      </c>
+      <c r="E52" t="s">
+        <v>3967</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>3968</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3969</v>
+      </c>
+      <c r="C53" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D53" t="s">
+        <v>3970</v>
+      </c>
+      <c r="E53" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>3972</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3973</v>
+      </c>
+      <c r="C54" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D54" t="s">
+        <v>3974</v>
+      </c>
+      <c r="E54" t="s">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>3976</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3977</v>
+      </c>
+      <c r="C55" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D55" t="s">
+        <v>3978</v>
+      </c>
+      <c r="E55" t="s">
+        <v>3979</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>3980</v>
+      </c>
+      <c r="B56" t="s">
+        <v>3981</v>
+      </c>
+      <c r="C56" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D56" t="s">
+        <v>3982</v>
+      </c>
+      <c r="E56" t="s">
+        <v>3983</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>3984</v>
+      </c>
+      <c r="B57" t="s">
+        <v>3985</v>
+      </c>
+      <c r="C57" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D57" t="s">
+        <v>3986</v>
+      </c>
+      <c r="E57" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>3988</v>
+      </c>
+      <c r="B58" t="s">
+        <v>3989</v>
+      </c>
+      <c r="C58" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D58" t="s">
+        <v>3990</v>
+      </c>
+      <c r="E58" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>3992</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3993</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D59" t="s">
+        <v>3994</v>
+      </c>
+      <c r="E59" t="s">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>3996</v>
+      </c>
+      <c r="B60" t="s">
+        <v>3997</v>
+      </c>
+      <c r="C60" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D60" t="s">
+        <v>3998</v>
+      </c>
+      <c r="E60" t="s">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>4000</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4001</v>
+      </c>
+      <c r="C61" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D61" t="s">
+        <v>4002</v>
+      </c>
+      <c r="E61" t="s">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>4004</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4005</v>
+      </c>
+      <c r="C62" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D62" t="s">
+        <v>4006</v>
+      </c>
+      <c r="E62" t="s">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>4008</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4009</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D63" t="s">
+        <v>4010</v>
+      </c>
+      <c r="E63" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D64" t="s">
+        <v>4014</v>
+      </c>
+      <c r="E64" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>4016</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4017</v>
+      </c>
+      <c r="C65" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D65" t="s">
+        <v>4018</v>
+      </c>
+      <c r="E65" t="s">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>4020</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4021</v>
+      </c>
+      <c r="C66" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D66" t="s">
+        <v>4022</v>
+      </c>
+      <c r="E66" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>4024</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4025</v>
+      </c>
+      <c r="C67" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D67" t="s">
+        <v>4026</v>
+      </c>
+      <c r="E67" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>4028</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4029</v>
+      </c>
+      <c r="C68" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D68" t="s">
+        <v>4030</v>
+      </c>
+      <c r="E68" t="s">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>4032</v>
+      </c>
+      <c r="B69" t="s">
+        <v>3890</v>
+      </c>
+      <c r="C69" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D69" t="s">
+        <v>3891</v>
+      </c>
+      <c r="E69" t="s">
+        <v>4034</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>4035</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4036</v>
+      </c>
+      <c r="C70" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D70" t="s">
+        <v>4037</v>
+      </c>
+      <c r="E70" t="s">
+        <v>4038</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>4039</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4040</v>
+      </c>
+      <c r="C71" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D71" t="s">
+        <v>4041</v>
+      </c>
+      <c r="E71" t="s">
+        <v>4042</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>4043</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4044</v>
+      </c>
+      <c r="C72" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D72" t="s">
+        <v>4045</v>
+      </c>
+      <c r="E72" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4048</v>
+      </c>
+      <c r="C73" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D73" t="s">
+        <v>4049</v>
+      </c>
+      <c r="E73" t="s">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>4051</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4052</v>
+      </c>
+      <c r="C74" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D74" t="s">
+        <v>4053</v>
+      </c>
+      <c r="E74" t="s">
+        <v>4054</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>4055</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4056</v>
+      </c>
+      <c r="C75" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D75" t="s">
+        <v>4057</v>
+      </c>
+      <c r="E75" t="s">
+        <v>4058</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>4059</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4060</v>
+      </c>
+      <c r="C76" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D76" t="s">
+        <v>4061</v>
+      </c>
+      <c r="E76" t="s">
+        <v>4062</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>4063</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4064</v>
+      </c>
+      <c r="C77" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D77" t="s">
+        <v>4065</v>
+      </c>
+      <c r="E77" t="s">
+        <v>4066</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>4067</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4068</v>
+      </c>
+      <c r="C78" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D78" t="s">
+        <v>4069</v>
+      </c>
+      <c r="E78" t="s">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>4071</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4072</v>
+      </c>
+      <c r="C79" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D79" t="s">
+        <v>4073</v>
+      </c>
+      <c r="E79" t="s">
+        <v>4074</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>4075</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4076</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D80" t="s">
+        <v>4077</v>
+      </c>
+      <c r="E80" t="s">
+        <v>4078</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>4079</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4080</v>
+      </c>
+      <c r="C81" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D81" t="s">
+        <v>4081</v>
+      </c>
+      <c r="E81" t="s">
+        <v>4082</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>4083</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4084</v>
+      </c>
+      <c r="C82" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D82" t="s">
+        <v>4085</v>
+      </c>
+      <c r="E82" t="s">
+        <v>4086</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>4087</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4088</v>
+      </c>
+      <c r="C83" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D83" t="s">
+        <v>4089</v>
+      </c>
+      <c r="E83" t="s">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>4091</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4092</v>
+      </c>
+      <c r="C84" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D84" t="s">
+        <v>4093</v>
+      </c>
+      <c r="E84" t="s">
+        <v>4094</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>4095</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4096</v>
+      </c>
+      <c r="C85" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D85" t="s">
+        <v>4097</v>
+      </c>
+      <c r="E85" t="s">
+        <v>4098</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>4099</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4100</v>
+      </c>
+      <c r="C86" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D86" t="s">
+        <v>4101</v>
+      </c>
+      <c r="E86" t="s">
+        <v>4102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>4103</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4104</v>
+      </c>
+      <c r="C87" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D87" t="s">
+        <v>4105</v>
+      </c>
+      <c r="E87" t="s">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>4107</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4108</v>
+      </c>
+      <c r="C88" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D88" t="s">
+        <v>4109</v>
+      </c>
+      <c r="E88" t="s">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>4111</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4112</v>
+      </c>
+      <c r="C89" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D89" t="s">
+        <v>4113</v>
+      </c>
+      <c r="E89" t="s">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>4115</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4116</v>
+      </c>
+      <c r="C90" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D90" t="s">
+        <v>4117</v>
+      </c>
+      <c r="E90" t="s">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>4119</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4120</v>
+      </c>
+      <c r="C91" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D91" t="s">
+        <v>4121</v>
+      </c>
+      <c r="E91" t="s">
+        <v>4122</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>4123</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4124</v>
+      </c>
+      <c r="C92" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D92" t="s">
+        <v>4125</v>
+      </c>
+      <c r="E92" t="s">
+        <v>4126</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>4127</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4128</v>
+      </c>
+      <c r="C93" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D93" t="s">
+        <v>4129</v>
+      </c>
+      <c r="E93" t="s">
+        <v>4130</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>4131</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4132</v>
+      </c>
+      <c r="C94" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D94" t="s">
+        <v>4133</v>
+      </c>
+      <c r="E94" t="s">
+        <v>4134</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>4135</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4136</v>
+      </c>
+      <c r="C95" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D95" t="s">
+        <v>4137</v>
+      </c>
+      <c r="E95" t="s">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>4139</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4140</v>
+      </c>
+      <c r="C96" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D96" t="s">
+        <v>4141</v>
+      </c>
+      <c r="E96" t="s">
+        <v>4142</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>4143</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4144</v>
+      </c>
+      <c r="C97" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D97" t="s">
+        <v>4145</v>
+      </c>
+      <c r="E97" t="s">
+        <v>4146</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>4147</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4148</v>
+      </c>
+      <c r="C98" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D98" t="s">
+        <v>4149</v>
+      </c>
+      <c r="E98" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>4151</v>
+      </c>
+      <c r="B99" t="s">
+        <v>4152</v>
+      </c>
+      <c r="C99" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D99" t="s">
+        <v>4153</v>
+      </c>
+      <c r="E99" t="s">
+        <v>4154</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>4155</v>
+      </c>
+      <c r="B100" t="s">
+        <v>4156</v>
+      </c>
+      <c r="C100" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D100" t="s">
+        <v>4157</v>
+      </c>
+      <c r="E100" t="s">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>4159</v>
+      </c>
+      <c r="B101" t="s">
+        <v>4160</v>
+      </c>
+      <c r="C101" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D101" t="s">
+        <v>4161</v>
+      </c>
+      <c r="E101" t="s">
+        <v>4162</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>4163</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4164</v>
+      </c>
+      <c r="C102" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D102" t="s">
+        <v>4165</v>
+      </c>
+      <c r="E102" t="s">
+        <v>4166</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>4167</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4168</v>
+      </c>
+      <c r="C103" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D103" t="s">
+        <v>4169</v>
+      </c>
+      <c r="E103" t="s">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>4171</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4172</v>
+      </c>
+      <c r="C104" t="s">
+        <v>4173</v>
+      </c>
+      <c r="D104" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E104" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>4176</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4177</v>
+      </c>
+      <c r="C105" t="s">
+        <v>4178</v>
+      </c>
+      <c r="D105" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E105" t="s">
+        <v>4179</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>4180</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4181</v>
+      </c>
+      <c r="C106" t="s">
+        <v>4182</v>
+      </c>
+      <c r="D106" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E106" t="s">
+        <v>4183</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>4184</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4185</v>
+      </c>
+      <c r="C107" t="s">
+        <v>4186</v>
+      </c>
+      <c r="D107" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E107" t="s">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>4188</v>
+      </c>
+      <c r="B108" t="s">
+        <v>4189</v>
+      </c>
+      <c r="C108" t="s">
+        <v>4190</v>
+      </c>
+      <c r="D108" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E108" t="s">
+        <v>4191</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>4192</v>
+      </c>
+      <c r="B109" t="s">
+        <v>4193</v>
+      </c>
+      <c r="C109" t="s">
+        <v>4194</v>
+      </c>
+      <c r="D109" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E109" t="s">
+        <v>4195</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>4196</v>
+      </c>
+      <c r="B110" t="s">
+        <v>4197</v>
+      </c>
+      <c r="C110" t="s">
+        <v>4198</v>
+      </c>
+      <c r="D110" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E110" t="s">
+        <v>4199</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>4200</v>
+      </c>
+      <c r="B111" t="s">
+        <v>4201</v>
+      </c>
+      <c r="C111" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D111" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E111" t="s">
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>4204</v>
+      </c>
+      <c r="B112" t="s">
+        <v>4205</v>
+      </c>
+      <c r="C112" t="s">
+        <v>4206</v>
+      </c>
+      <c r="D112" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E112" t="s">
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>4208</v>
+      </c>
+      <c r="B113" t="s">
+        <v>4209</v>
+      </c>
+      <c r="C113" t="s">
+        <v>4210</v>
+      </c>
+      <c r="D113" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E113" t="s">
+        <v>4211</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>4212</v>
+      </c>
+      <c r="B114" t="s">
+        <v>4213</v>
+      </c>
+      <c r="C114" t="s">
+        <v>4214</v>
+      </c>
+      <c r="D114" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E114" t="s">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>4216</v>
+      </c>
+      <c r="B115" t="s">
+        <v>4217</v>
+      </c>
+      <c r="C115" t="s">
+        <v>4218</v>
+      </c>
+      <c r="D115" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E115" t="s">
+        <v>4219</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>4220</v>
+      </c>
+      <c r="B116" t="s">
+        <v>4221</v>
+      </c>
+      <c r="C116" t="s">
+        <v>4222</v>
+      </c>
+      <c r="D116" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E116" t="s">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>4224</v>
+      </c>
+      <c r="B117" t="s">
+        <v>4225</v>
+      </c>
+      <c r="C117" t="s">
+        <v>4226</v>
+      </c>
+      <c r="D117" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E117" t="s">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>4228</v>
+      </c>
+      <c r="B118" t="s">
+        <v>4229</v>
+      </c>
+      <c r="C118" t="s">
+        <v>4230</v>
+      </c>
+      <c r="D118" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E118" t="s">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>4232</v>
+      </c>
+      <c r="B119" t="s">
+        <v>4233</v>
+      </c>
+      <c r="C119" t="s">
+        <v>4234</v>
+      </c>
+      <c r="D119" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E119" t="s">
+        <v>4235</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>4236</v>
+      </c>
+      <c r="B120" t="s">
+        <v>4237</v>
+      </c>
+      <c r="C120" t="s">
+        <v>4238</v>
+      </c>
+      <c r="D120" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E120" t="s">
+        <v>4239</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>4240</v>
+      </c>
+      <c r="B121" t="s">
+        <v>4241</v>
+      </c>
+      <c r="C121" t="s">
+        <v>4242</v>
+      </c>
+      <c r="D121" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E121" t="s">
+        <v>4243</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>4244</v>
+      </c>
+      <c r="B122" t="s">
+        <v>4245</v>
+      </c>
+      <c r="C122" t="s">
+        <v>4246</v>
+      </c>
+      <c r="D122" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E122" t="s">
+        <v>4247</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>4248</v>
+      </c>
+      <c r="B123" t="s">
+        <v>4249</v>
+      </c>
+      <c r="C123" t="s">
+        <v>4250</v>
+      </c>
+      <c r="D123" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E123" t="s">
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>4252</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4253</v>
+      </c>
+      <c r="C124" t="s">
+        <v>4254</v>
+      </c>
+      <c r="D124" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E124" t="s">
+        <v>4255</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>4256</v>
+      </c>
+      <c r="B125" t="s">
+        <v>4257</v>
+      </c>
+      <c r="C125" t="s">
+        <v>4258</v>
+      </c>
+      <c r="D125" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E125" t="s">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>4260</v>
+      </c>
+      <c r="B126" t="s">
+        <v>4261</v>
+      </c>
+      <c r="C126" t="s">
+        <v>4262</v>
+      </c>
+      <c r="D126" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E126" t="s">
+        <v>4263</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>4264</v>
+      </c>
+      <c r="B127" t="s">
+        <v>4265</v>
+      </c>
+      <c r="C127" t="s">
+        <v>4266</v>
+      </c>
+      <c r="D127" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E127" t="s">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
+        <v>4268</v>
+      </c>
+      <c r="B128" t="s">
+        <v>4172</v>
+      </c>
+      <c r="C128" t="s">
+        <v>4173</v>
+      </c>
+      <c r="D128" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E128" t="s">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
+        <v>4271</v>
+      </c>
+      <c r="B129" t="s">
+        <v>4177</v>
+      </c>
+      <c r="C129" t="s">
+        <v>4178</v>
+      </c>
+      <c r="D129" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E129" t="s">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
+        <v>4273</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4181</v>
+      </c>
+      <c r="C130" t="s">
+        <v>4182</v>
+      </c>
+      <c r="D130" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E130" t="s">
+        <v>4274</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
+        <v>4275</v>
+      </c>
+      <c r="B131" t="s">
+        <v>4185</v>
+      </c>
+      <c r="C131" t="s">
+        <v>4186</v>
+      </c>
+      <c r="D131" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E131" t="s">
+        <v>4276</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
+        <v>4277</v>
+      </c>
+      <c r="B132" t="s">
+        <v>4189</v>
+      </c>
+      <c r="C132" t="s">
+        <v>4190</v>
+      </c>
+      <c r="D132" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E132" t="s">
+        <v>4278</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
+        <v>4279</v>
+      </c>
+      <c r="B133" t="s">
+        <v>4193</v>
+      </c>
+      <c r="C133" t="s">
+        <v>4194</v>
+      </c>
+      <c r="D133" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E133" t="s">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
+        <v>4281</v>
+      </c>
+      <c r="B134" t="s">
+        <v>4197</v>
+      </c>
+      <c r="C134" t="s">
+        <v>4198</v>
+      </c>
+      <c r="D134" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E134" t="s">
+        <v>4282</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
+        <v>4283</v>
+      </c>
+      <c r="B135" t="s">
+        <v>4201</v>
+      </c>
+      <c r="C135" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D135" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E135" t="s">
+        <v>4284</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
+        <v>4285</v>
+      </c>
+      <c r="B136" t="s">
+        <v>4205</v>
+      </c>
+      <c r="C136" t="s">
+        <v>4206</v>
+      </c>
+      <c r="D136" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E136" t="s">
+        <v>4286</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
+        <v>4287</v>
+      </c>
+      <c r="B137" t="s">
+        <v>4209</v>
+      </c>
+      <c r="C137" t="s">
+        <v>4210</v>
+      </c>
+      <c r="D137" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E137" t="s">
+        <v>4288</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
+        <v>4289</v>
+      </c>
+      <c r="B138" t="s">
+        <v>4213</v>
+      </c>
+      <c r="C138" t="s">
+        <v>4214</v>
+      </c>
+      <c r="D138" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E138" t="s">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>4291</v>
+      </c>
+      <c r="B139" t="s">
+        <v>4217</v>
+      </c>
+      <c r="C139" t="s">
+        <v>4218</v>
+      </c>
+      <c r="D139" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E139" t="s">
+        <v>4292</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>4293</v>
+      </c>
+      <c r="B140" t="s">
+        <v>4221</v>
+      </c>
+      <c r="C140" t="s">
+        <v>4222</v>
+      </c>
+      <c r="D140" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E140" t="s">
+        <v>4294</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
+        <v>4295</v>
+      </c>
+      <c r="B141" t="s">
+        <v>4225</v>
+      </c>
+      <c r="C141" t="s">
+        <v>4226</v>
+      </c>
+      <c r="D141" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E141" t="s">
+        <v>4296</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
+        <v>4297</v>
+      </c>
+      <c r="B142" t="s">
+        <v>4229</v>
+      </c>
+      <c r="C142" t="s">
+        <v>4230</v>
+      </c>
+      <c r="D142" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E142" t="s">
+        <v>4298</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
+        <v>4299</v>
+      </c>
+      <c r="B143" t="s">
+        <v>4233</v>
+      </c>
+      <c r="C143" t="s">
+        <v>4234</v>
+      </c>
+      <c r="D143" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E143" t="s">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
+        <v>4301</v>
+      </c>
+      <c r="B144" t="s">
+        <v>4237</v>
+      </c>
+      <c r="C144" t="s">
+        <v>4238</v>
+      </c>
+      <c r="D144" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E144" t="s">
+        <v>4302</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
+        <v>4303</v>
+      </c>
+      <c r="B145" t="s">
+        <v>4241</v>
+      </c>
+      <c r="C145" t="s">
+        <v>4242</v>
+      </c>
+      <c r="D145" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E145" t="s">
+        <v>4304</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
+        <v>4305</v>
+      </c>
+      <c r="B146" t="s">
+        <v>4245</v>
+      </c>
+      <c r="C146" t="s">
+        <v>4246</v>
+      </c>
+      <c r="D146" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E146" t="s">
+        <v>4306</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
+        <v>4307</v>
+      </c>
+      <c r="B147" t="s">
+        <v>4249</v>
+      </c>
+      <c r="C147" t="s">
+        <v>4250</v>
+      </c>
+      <c r="D147" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E147" t="s">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B148" t="s">
+        <v>4253</v>
+      </c>
+      <c r="C148" t="s">
+        <v>4254</v>
+      </c>
+      <c r="D148" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E148" t="s">
+        <v>4310</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
+        <v>4311</v>
+      </c>
+      <c r="B149" t="s">
+        <v>4257</v>
+      </c>
+      <c r="C149" t="s">
+        <v>4258</v>
+      </c>
+      <c r="D149" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E149" t="s">
+        <v>4312</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
+        <v>4313</v>
+      </c>
+      <c r="B150" t="s">
+        <v>4261</v>
+      </c>
+      <c r="C150" t="s">
+        <v>4262</v>
+      </c>
+      <c r="D150" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E150" t="s">
+        <v>4314</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
+        <v>4315</v>
+      </c>
+      <c r="B151" t="s">
+        <v>4265</v>
+      </c>
+      <c r="C151" t="s">
+        <v>4266</v>
+      </c>
+      <c r="D151" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E151" t="s">
+        <v>4316</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
+        <v>4317</v>
+      </c>
+      <c r="B152" t="s">
+        <v>4318</v>
+      </c>
+      <c r="C152" t="s">
+        <v>4319</v>
+      </c>
+      <c r="D152" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E152" t="s">
+        <v>4321</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
+        <v>4322</v>
+      </c>
+      <c r="B153" t="s">
+        <v>4323</v>
+      </c>
+      <c r="C153" t="s">
+        <v>4324</v>
+      </c>
+      <c r="D153" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E153" t="s">
+        <v>4325</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
+        <v>4326</v>
+      </c>
+      <c r="B154" t="s">
+        <v>4327</v>
+      </c>
+      <c r="C154" t="s">
+        <v>4328</v>
+      </c>
+      <c r="D154" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E154" t="s">
+        <v>4329</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
+        <v>4330</v>
+      </c>
+      <c r="B155" t="s">
+        <v>4331</v>
+      </c>
+      <c r="C155" t="s">
+        <v>4332</v>
+      </c>
+      <c r="D155" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E155" t="s">
+        <v>4333</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>4334</v>
+      </c>
+      <c r="B156" t="s">
+        <v>4335</v>
+      </c>
+      <c r="C156" t="s">
+        <v>4336</v>
+      </c>
+      <c r="D156" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E156" t="s">
+        <v>4337</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
+        <v>4338</v>
+      </c>
+      <c r="B157" t="s">
+        <v>4339</v>
+      </c>
+      <c r="C157" t="s">
+        <v>4340</v>
+      </c>
+      <c r="D157" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E157" t="s">
+        <v>4341</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
+        <v>4342</v>
+      </c>
+      <c r="B158" t="s">
+        <v>4343</v>
+      </c>
+      <c r="C158" t="s">
+        <v>4344</v>
+      </c>
+      <c r="D158" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E158" t="s">
+        <v>4345</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
+        <v>4346</v>
+      </c>
+      <c r="B159" t="s">
+        <v>4347</v>
+      </c>
+      <c r="C159" t="s">
+        <v>4348</v>
+      </c>
+      <c r="D159" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E159" t="s">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
+        <v>4350</v>
+      </c>
+      <c r="B160" t="s">
+        <v>4351</v>
+      </c>
+      <c r="C160" t="s">
+        <v>4352</v>
+      </c>
+      <c r="D160" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E160" t="s">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
+        <v>4354</v>
+      </c>
+      <c r="B161" t="s">
+        <v>4355</v>
+      </c>
+      <c r="C161" t="s">
+        <v>4356</v>
+      </c>
+      <c r="D161" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E161" t="s">
+        <v>4357</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
+        <v>4358</v>
+      </c>
+      <c r="B162" t="s">
+        <v>4359</v>
+      </c>
+      <c r="C162" t="s">
+        <v>4360</v>
+      </c>
+      <c r="D162" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E162" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
+        <v>4362</v>
+      </c>
+      <c r="B163" t="s">
+        <v>4363</v>
+      </c>
+      <c r="C163" t="s">
+        <v>4364</v>
+      </c>
+      <c r="D163" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E163" t="s">
+        <v>4365</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
+        <v>4366</v>
+      </c>
+      <c r="B164" t="s">
+        <v>4367</v>
+      </c>
+      <c r="C164" t="s">
+        <v>4368</v>
+      </c>
+      <c r="D164" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E164" t="s">
+        <v>4369</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
+        <v>4370</v>
+      </c>
+      <c r="B165" t="s">
+        <v>4371</v>
+      </c>
+      <c r="C165" t="s">
+        <v>4372</v>
+      </c>
+      <c r="D165" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E165" t="s">
+        <v>4373</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
+        <v>4374</v>
+      </c>
+      <c r="B166" t="s">
+        <v>4375</v>
+      </c>
+      <c r="C166" t="s">
+        <v>4376</v>
+      </c>
+      <c r="D166" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E166" t="s">
+        <v>4377</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
+        <v>4378</v>
+      </c>
+      <c r="B167" t="s">
+        <v>4379</v>
+      </c>
+      <c r="C167" t="s">
+        <v>4380</v>
+      </c>
+      <c r="D167" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E167" t="s">
+        <v>4381</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
+        <v>4382</v>
+      </c>
+      <c r="B168" t="s">
+        <v>4383</v>
+      </c>
+      <c r="C168" t="s">
+        <v>4384</v>
+      </c>
+      <c r="D168" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E168" t="s">
+        <v>4385</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
+        <v>4386</v>
+      </c>
+      <c r="B169" t="s">
+        <v>4387</v>
+      </c>
+      <c r="C169" t="s">
+        <v>4388</v>
+      </c>
+      <c r="D169" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E169" t="s">
+        <v>4389</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
+        <v>4390</v>
+      </c>
+      <c r="B170" t="s">
+        <v>4391</v>
+      </c>
+      <c r="C170" t="s">
+        <v>4392</v>
+      </c>
+      <c r="D170" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E170" t="s">
+        <v>4393</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
+        <v>4394</v>
+      </c>
+      <c r="B171" t="s">
+        <v>4395</v>
+      </c>
+      <c r="C171" t="s">
+        <v>4396</v>
+      </c>
+      <c r="D171" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E171" t="s">
+        <v>4397</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
+        <v>4398</v>
+      </c>
+      <c r="B172" t="s">
+        <v>4399</v>
+      </c>
+      <c r="C172" t="s">
+        <v>4400</v>
+      </c>
+      <c r="D172" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E172" t="s">
+        <v>4401</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
+        <v>4402</v>
+      </c>
+      <c r="B173" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C173" t="s">
+        <v>4404</v>
+      </c>
+      <c r="D173" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E173" t="s">
+        <v>4405</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
+        <v>4406</v>
+      </c>
+      <c r="B174" t="s">
+        <v>4407</v>
+      </c>
+      <c r="C174" t="s">
+        <v>4408</v>
+      </c>
+      <c r="D174" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E174" t="s">
+        <v>4409</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
+        <v>4410</v>
+      </c>
+      <c r="B175" t="s">
+        <v>4411</v>
+      </c>
+      <c r="C175" t="s">
+        <v>4412</v>
+      </c>
+      <c r="D175" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E175" t="s">
+        <v>4413</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
+        <v>4414</v>
+      </c>
+      <c r="B176" t="s">
+        <v>4415</v>
+      </c>
+      <c r="C176" t="s">
+        <v>4416</v>
+      </c>
+      <c r="D176" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E176" t="str">
+        <f>C176&amp;D176</f>
+        <v>AGACGACGTGGAGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
+        <v>4417</v>
+      </c>
+      <c r="B177" t="s">
+        <v>4418</v>
+      </c>
+      <c r="C177" t="s">
+        <v>4419</v>
+      </c>
+      <c r="D177" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E177" t="str">
+        <f t="shared" ref="E177:E240" si="0">C177&amp;D177</f>
+        <v>ACTTCATCGTATGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
+        <v>4420</v>
+      </c>
+      <c r="B178" t="s">
+        <v>4421</v>
+      </c>
+      <c r="C178" t="s">
+        <v>4422</v>
+      </c>
+      <c r="D178" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E178" t="str">
+        <f t="shared" si="0"/>
+        <v>TGTGATCTTTACGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
+        <v>4423</v>
+      </c>
+      <c r="B179" t="s">
+        <v>4424</v>
+      </c>
+      <c r="C179" t="s">
+        <v>4425</v>
+      </c>
+      <c r="D179" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E179" t="str">
+        <f t="shared" si="0"/>
+        <v>TCCTCCGGTTGGGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
+        <v>4426</v>
+      </c>
+      <c r="B180" t="s">
+        <v>4427</v>
+      </c>
+      <c r="C180" t="s">
+        <v>4428</v>
+      </c>
+      <c r="D180" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E180" t="str">
+        <f t="shared" si="0"/>
+        <v>AACTTCACTTCCGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
+        <v>4429</v>
+      </c>
+      <c r="B181" t="s">
+        <v>4430</v>
+      </c>
+      <c r="C181" t="s">
+        <v>4431</v>
+      </c>
+      <c r="D181" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E181" t="str">
+        <f t="shared" si="0"/>
+        <v>CGACCGGTGAAGGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
+        <v>4432</v>
+      </c>
+      <c r="B182" t="s">
+        <v>4433</v>
+      </c>
+      <c r="C182" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D182" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E182" t="str">
+        <f t="shared" si="0"/>
+        <v>CCTCTCGGGTTGGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
+        <v>4435</v>
+      </c>
+      <c r="B183" t="s">
+        <v>4436</v>
+      </c>
+      <c r="C183" t="s">
+        <v>4437</v>
+      </c>
+      <c r="D183" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E183" t="str">
+        <f t="shared" si="0"/>
+        <v>GATGGCGGACTGGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
+        <v>4438</v>
+      </c>
+      <c r="B184" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C184" t="s">
+        <v>4440</v>
+      </c>
+      <c r="D184" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E184" t="str">
+        <f t="shared" si="0"/>
+        <v>ATCTTGGAGTCGGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B185" t="s">
+        <v>4442</v>
+      </c>
+      <c r="C185" t="s">
+        <v>4443</v>
+      </c>
+      <c r="D185" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E185" t="str">
+        <f t="shared" si="0"/>
+        <v>TGCCCTCCGTAGGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
+        <v>4444</v>
+      </c>
+      <c r="B186" t="s">
+        <v>4445</v>
+      </c>
+      <c r="C186" t="s">
+        <v>4446</v>
+      </c>
+      <c r="D186" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E186" t="str">
+        <f t="shared" si="0"/>
+        <v>GTTGTGGGCGCGGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
+        <v>4447</v>
+      </c>
+      <c r="B187" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C187" t="s">
+        <v>4449</v>
+      </c>
+      <c r="D187" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E187" t="str">
+        <f t="shared" si="0"/>
+        <v>ACCACCGTAACCGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
+        <v>4450</v>
+      </c>
+      <c r="B188" t="s">
+        <v>4451</v>
+      </c>
+      <c r="C188" t="s">
+        <v>4452</v>
+      </c>
+      <c r="D188" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E188" t="str">
+        <f t="shared" si="0"/>
+        <v>AGGAAGTAACTTGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
+        <v>4453</v>
+      </c>
+      <c r="B189" t="s">
+        <v>4454</v>
+      </c>
+      <c r="C189" t="s">
+        <v>4455</v>
+      </c>
+      <c r="D189" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E189" t="str">
+        <f t="shared" si="0"/>
+        <v>CGTTCGCTAGCCGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
+        <v>4456</v>
+      </c>
+      <c r="B190" t="s">
+        <v>4457</v>
+      </c>
+      <c r="C190" t="s">
+        <v>4458</v>
+      </c>
+      <c r="D190" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E190" t="str">
+        <f t="shared" si="0"/>
+        <v>CTCACCTAGGAAGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
+        <v>4459</v>
+      </c>
+      <c r="B191" t="s">
+        <v>4460</v>
+      </c>
+      <c r="C191" t="s">
+        <v>4461</v>
+      </c>
+      <c r="D191" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E191" t="str">
+        <f t="shared" si="0"/>
+        <v>AGATGCAATGATGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
+        <v>4462</v>
+      </c>
+      <c r="B192" t="s">
+        <v>4463</v>
+      </c>
+      <c r="C192" t="s">
+        <v>4464</v>
+      </c>
+      <c r="D192" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E192" t="str">
+        <f t="shared" si="0"/>
+        <v>GCATTCGGCGTTGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
+        <v>4465</v>
+      </c>
+      <c r="B193" t="s">
+        <v>4466</v>
+      </c>
+      <c r="C193" t="s">
+        <v>4467</v>
+      </c>
+      <c r="D193" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E193" t="str">
+        <f t="shared" si="0"/>
+        <v>TCTACATACATAGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B194" t="s">
+        <v>4469</v>
+      </c>
+      <c r="C194" t="s">
+        <v>4470</v>
+      </c>
+      <c r="D194" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E194" t="str">
+        <f t="shared" si="0"/>
+        <v>GAGTCTTGGTAAGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B195" t="s">
+        <v>4472</v>
+      </c>
+      <c r="C195" t="s">
+        <v>4473</v>
+      </c>
+      <c r="D195" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E195" t="str">
+        <f t="shared" si="0"/>
+        <v>CAGTCTAGTACGGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
+        <v>4474</v>
+      </c>
+      <c r="B196" t="s">
+        <v>4475</v>
+      </c>
+      <c r="C196" t="s">
+        <v>4476</v>
+      </c>
+      <c r="D196" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E196" t="str">
+        <f t="shared" si="0"/>
+        <v>GTTCGAGTGAATGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
+        <v>4477</v>
+      </c>
+      <c r="B197" t="s">
+        <v>4478</v>
+      </c>
+      <c r="C197" t="s">
+        <v>4479</v>
+      </c>
+      <c r="D197" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E197" t="str">
+        <f t="shared" si="0"/>
+        <v>AGTCCGAGTTGTGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
+        <v>4480</v>
+      </c>
+      <c r="B198" t="s">
+        <v>4481</v>
+      </c>
+      <c r="C198" t="s">
+        <v>4482</v>
+      </c>
+      <c r="D198" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E198" t="str">
+        <f t="shared" si="0"/>
+        <v>CGTGAGGACCAGGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" t="s">
+        <v>4483</v>
+      </c>
+      <c r="B199" t="s">
+        <v>4484</v>
+      </c>
+      <c r="C199" t="s">
+        <v>4485</v>
+      </c>
+      <c r="D199" t="s">
+        <v>4174</v>
+      </c>
+      <c r="E199" t="str">
+        <f t="shared" si="0"/>
+        <v>CGGTTGGCGGGTGTGTTTCAAGCAGGCAGTCG</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
+        <v>4486</v>
+      </c>
+      <c r="B200" t="s">
+        <v>4415</v>
+      </c>
+      <c r="C200" t="s">
+        <v>4416</v>
+      </c>
+      <c r="D200" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E200" t="str">
+        <f t="shared" si="0"/>
+        <v>AGACGACGTGGAGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" t="s">
+        <v>4487</v>
+      </c>
+      <c r="B201" t="s">
+        <v>4418</v>
+      </c>
+      <c r="C201" t="s">
+        <v>4419</v>
+      </c>
+      <c r="D201" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E201" t="str">
+        <f t="shared" si="0"/>
+        <v>ACTTCATCGTATGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" t="s">
+        <v>4488</v>
+      </c>
+      <c r="B202" t="s">
+        <v>4421</v>
+      </c>
+      <c r="C202" t="s">
+        <v>4422</v>
+      </c>
+      <c r="D202" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E202" t="str">
+        <f t="shared" si="0"/>
+        <v>TGTGATCTTTACGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
+        <v>4489</v>
+      </c>
+      <c r="B203" t="s">
+        <v>4424</v>
+      </c>
+      <c r="C203" t="s">
+        <v>4425</v>
+      </c>
+      <c r="D203" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E203" t="str">
+        <f t="shared" si="0"/>
+        <v>TCCTCCGGTTGGGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" t="s">
+        <v>4490</v>
+      </c>
+      <c r="B204" t="s">
+        <v>4427</v>
+      </c>
+      <c r="C204" t="s">
+        <v>4428</v>
+      </c>
+      <c r="D204" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E204" t="str">
+        <f t="shared" si="0"/>
+        <v>AACTTCACTTCCGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" t="s">
+        <v>4491</v>
+      </c>
+      <c r="B205" t="s">
+        <v>4430</v>
+      </c>
+      <c r="C205" t="s">
+        <v>4431</v>
+      </c>
+      <c r="D205" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E205" t="str">
+        <f t="shared" si="0"/>
+        <v>CGACCGGTGAAGGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
+        <v>4492</v>
+      </c>
+      <c r="B206" t="s">
+        <v>4433</v>
+      </c>
+      <c r="C206" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D206" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E206" t="str">
+        <f t="shared" si="0"/>
+        <v>CCTCTCGGGTTGGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B207" t="s">
+        <v>4436</v>
+      </c>
+      <c r="C207" t="s">
+        <v>4437</v>
+      </c>
+      <c r="D207" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E207" t="str">
+        <f t="shared" si="0"/>
+        <v>GATGGCGGACTGGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
+        <v>4494</v>
+      </c>
+      <c r="B208" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C208" t="s">
+        <v>4440</v>
+      </c>
+      <c r="D208" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E208" t="str">
+        <f t="shared" si="0"/>
+        <v>ATCTTGGAGTCGGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" t="s">
+        <v>4495</v>
+      </c>
+      <c r="B209" t="s">
+        <v>4442</v>
+      </c>
+      <c r="C209" t="s">
+        <v>4443</v>
+      </c>
+      <c r="D209" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E209" t="str">
+        <f t="shared" si="0"/>
+        <v>TGCCCTCCGTAGGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" t="s">
+        <v>4496</v>
+      </c>
+      <c r="B210" t="s">
+        <v>4445</v>
+      </c>
+      <c r="C210" t="s">
+        <v>4446</v>
+      </c>
+      <c r="D210" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E210" t="str">
+        <f t="shared" si="0"/>
+        <v>GTTGTGGGCGCGGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" t="s">
+        <v>4497</v>
+      </c>
+      <c r="B211" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C211" t="s">
+        <v>4449</v>
+      </c>
+      <c r="D211" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E211" t="str">
+        <f t="shared" si="0"/>
+        <v>ACCACCGTAACCGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" t="s">
+        <v>4498</v>
+      </c>
+      <c r="B212" t="s">
+        <v>4451</v>
+      </c>
+      <c r="C212" t="s">
+        <v>4452</v>
+      </c>
+      <c r="D212" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E212" t="str">
+        <f t="shared" si="0"/>
+        <v>AGGAAGTAACTTGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" t="s">
+        <v>4499</v>
+      </c>
+      <c r="B213" t="s">
+        <v>4454</v>
+      </c>
+      <c r="C213" t="s">
+        <v>4455</v>
+      </c>
+      <c r="D213" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E213" t="str">
+        <f t="shared" si="0"/>
+        <v>CGTTCGCTAGCCGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" t="s">
+        <v>4500</v>
+      </c>
+      <c r="B214" t="s">
+        <v>4457</v>
+      </c>
+      <c r="C214" t="s">
+        <v>4458</v>
+      </c>
+      <c r="D214" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E214" t="str">
+        <f t="shared" si="0"/>
+        <v>CTCACCTAGGAAGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" t="s">
+        <v>4501</v>
+      </c>
+      <c r="B215" t="s">
+        <v>4460</v>
+      </c>
+      <c r="C215" t="s">
+        <v>4461</v>
+      </c>
+      <c r="D215" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E215" t="str">
+        <f t="shared" si="0"/>
+        <v>AGATGCAATGATGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" t="s">
+        <v>4502</v>
+      </c>
+      <c r="B216" t="s">
+        <v>4463</v>
+      </c>
+      <c r="C216" t="s">
+        <v>4464</v>
+      </c>
+      <c r="D216" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E216" t="str">
+        <f t="shared" si="0"/>
+        <v>GCATTCGGCGTTGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" t="s">
+        <v>4503</v>
+      </c>
+      <c r="B217" t="s">
+        <v>4466</v>
+      </c>
+      <c r="C217" t="s">
+        <v>4467</v>
+      </c>
+      <c r="D217" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E217" t="str">
+        <f t="shared" si="0"/>
+        <v>TCTACATACATAGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" t="s">
+        <v>4504</v>
+      </c>
+      <c r="B218" t="s">
+        <v>4469</v>
+      </c>
+      <c r="C218" t="s">
+        <v>4470</v>
+      </c>
+      <c r="D218" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E218" t="str">
+        <f t="shared" si="0"/>
+        <v>GAGTCTTGGTAAGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" t="s">
+        <v>4505</v>
+      </c>
+      <c r="B219" t="s">
+        <v>4472</v>
+      </c>
+      <c r="C219" t="s">
+        <v>4473</v>
+      </c>
+      <c r="D219" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E219" t="str">
+        <f t="shared" si="0"/>
+        <v>CAGTCTAGTACGGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" t="s">
+        <v>4506</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4475</v>
+      </c>
+      <c r="C220" t="s">
+        <v>4476</v>
+      </c>
+      <c r="D220" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E220" t="str">
+        <f t="shared" si="0"/>
+        <v>GTTCGAGTGAATGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B221" t="s">
+        <v>4478</v>
+      </c>
+      <c r="C221" t="s">
+        <v>4479</v>
+      </c>
+      <c r="D221" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E221" t="str">
+        <f t="shared" si="0"/>
+        <v>AGTCCGAGTTGTGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" t="s">
+        <v>4508</v>
+      </c>
+      <c r="B222" t="s">
+        <v>4481</v>
+      </c>
+      <c r="C222" t="s">
+        <v>4482</v>
+      </c>
+      <c r="D222" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E222" t="str">
+        <f t="shared" si="0"/>
+        <v>CGTGAGGACCAGGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B223" t="s">
+        <v>4484</v>
+      </c>
+      <c r="C223" t="s">
+        <v>4485</v>
+      </c>
+      <c r="D223" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E223" t="str">
+        <f t="shared" si="0"/>
+        <v>CGGTTGGCGGGTGTGTTTCAAGCAGGCCGTCG</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" t="s">
+        <v>4510</v>
+      </c>
+      <c r="B224" t="s">
+        <v>4511</v>
+      </c>
+      <c r="C224" t="s">
+        <v>4512</v>
+      </c>
+      <c r="D224" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E224" t="str">
+        <f t="shared" si="0"/>
+        <v>CGATTCCTTAATTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" t="s">
+        <v>4513</v>
+      </c>
+      <c r="B225" t="s">
+        <v>4514</v>
+      </c>
+      <c r="C225" t="s">
+        <v>4515</v>
+      </c>
+      <c r="D225" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E225" t="str">
+        <f t="shared" si="0"/>
+        <v>TGCCTGCTCGACTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" t="s">
+        <v>4516</v>
+      </c>
+      <c r="B226" t="s">
+        <v>4517</v>
+      </c>
+      <c r="C226" t="s">
+        <v>4518</v>
+      </c>
+      <c r="D226" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E226" t="str">
+        <f t="shared" si="0"/>
+        <v>TACTGTACTGTTTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B227" t="s">
+        <v>4520</v>
+      </c>
+      <c r="C227" t="s">
+        <v>4521</v>
+      </c>
+      <c r="D227" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E227" t="str">
+        <f t="shared" si="0"/>
+        <v>TCTCGCACTGGATCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" t="s">
+        <v>4522</v>
+      </c>
+      <c r="B228" t="s">
+        <v>4523</v>
+      </c>
+      <c r="C228" t="s">
+        <v>4524</v>
+      </c>
+      <c r="D228" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E228" t="str">
+        <f t="shared" si="0"/>
+        <v>ACCAGTGACTCATCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" t="s">
+        <v>4525</v>
+      </c>
+      <c r="B229" t="s">
+        <v>4526</v>
+      </c>
+      <c r="C229" t="s">
+        <v>4527</v>
+      </c>
+      <c r="D229" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E229" t="str">
+        <f t="shared" si="0"/>
+        <v>TGGCGCACGGACTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" t="s">
+        <v>4528</v>
+      </c>
+      <c r="B230" t="s">
+        <v>4529</v>
+      </c>
+      <c r="C230" t="s">
+        <v>4530</v>
+      </c>
+      <c r="D230" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E230" t="str">
+        <f t="shared" si="0"/>
+        <v>CATTTACATCACTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" t="s">
+        <v>4531</v>
+      </c>
+      <c r="B231" t="s">
+        <v>4532</v>
+      </c>
+      <c r="C231" t="s">
+        <v>4533</v>
+      </c>
+      <c r="D231" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E231" t="str">
+        <f t="shared" si="0"/>
+        <v>GTGGGACTGCGCTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" t="s">
+        <v>4534</v>
+      </c>
+      <c r="B232" t="s">
+        <v>4535</v>
+      </c>
+      <c r="C232" t="s">
+        <v>4536</v>
+      </c>
+      <c r="D232" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E232" t="str">
+        <f t="shared" si="0"/>
+        <v>CGGCCTAAGTTCTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" t="s">
+        <v>4537</v>
+      </c>
+      <c r="B233" t="s">
+        <v>4538</v>
+      </c>
+      <c r="C233" t="s">
+        <v>4539</v>
+      </c>
+      <c r="D233" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E233" t="str">
+        <f t="shared" si="0"/>
+        <v>GCTGAGCCTTTGTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" t="s">
+        <v>4540</v>
+      </c>
+      <c r="B234" t="s">
+        <v>4541</v>
+      </c>
+      <c r="C234" t="s">
+        <v>4542</v>
+      </c>
+      <c r="D234" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E234" t="str">
+        <f t="shared" si="0"/>
+        <v>AGAGACGCGTAGTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" t="s">
+        <v>4543</v>
+      </c>
+      <c r="B235" t="s">
+        <v>4544</v>
+      </c>
+      <c r="C235" t="s">
+        <v>4545</v>
+      </c>
+      <c r="D235" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E235" t="str">
+        <f t="shared" si="0"/>
+        <v>CCACCGGGCCGATCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" t="s">
+        <v>4546</v>
+      </c>
+      <c r="B236" t="s">
+        <v>4547</v>
+      </c>
+      <c r="C236" t="s">
+        <v>4548</v>
+      </c>
+      <c r="D236" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E236" t="str">
+        <f t="shared" si="0"/>
+        <v>AATCCGGTCACCTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" t="s">
+        <v>4549</v>
+      </c>
+      <c r="B237" t="s">
+        <v>4550</v>
+      </c>
+      <c r="C237" t="s">
+        <v>4551</v>
+      </c>
+      <c r="D237" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E237" t="str">
+        <f t="shared" si="0"/>
+        <v>TCTTACCCATAATCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" t="s">
+        <v>4552</v>
+      </c>
+      <c r="B238" t="s">
+        <v>4553</v>
+      </c>
+      <c r="C238" t="s">
+        <v>4554</v>
+      </c>
+      <c r="D238" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E238" t="str">
+        <f t="shared" si="0"/>
+        <v>CTAGAGCTCCCATCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" t="s">
+        <v>4555</v>
+      </c>
+      <c r="B239" t="s">
+        <v>4556</v>
+      </c>
+      <c r="C239" t="s">
+        <v>4557</v>
+      </c>
+      <c r="D239" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E239" t="str">
+        <f t="shared" si="0"/>
+        <v>GGTCTTAGCACCTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" t="s">
+        <v>4558</v>
+      </c>
+      <c r="B240" t="s">
+        <v>4559</v>
+      </c>
+      <c r="C240" t="s">
+        <v>4560</v>
+      </c>
+      <c r="D240" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E240" t="str">
+        <f t="shared" si="0"/>
+        <v>GCCTACTCTCGGTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" t="s">
+        <v>4561</v>
+      </c>
+      <c r="B241" t="s">
+        <v>4562</v>
+      </c>
+      <c r="C241" t="s">
+        <v>4563</v>
+      </c>
+      <c r="D241" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E241" t="str">
+        <f t="shared" ref="E241:E247" si="1">C241&amp;D241</f>
+        <v>ACTGCCCGATACTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" t="s">
+        <v>4564</v>
+      </c>
+      <c r="B242" t="s">
+        <v>4565</v>
+      </c>
+      <c r="C242" t="s">
+        <v>4566</v>
+      </c>
+      <c r="D242" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E242" t="str">
+        <f t="shared" si="1"/>
+        <v>TTCTTAACGCCTTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" t="s">
+        <v>4567</v>
+      </c>
+      <c r="B243" t="s">
+        <v>4568</v>
+      </c>
+      <c r="C243" t="s">
+        <v>4569</v>
+      </c>
+      <c r="D243" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E243" t="str">
+        <f t="shared" si="1"/>
+        <v>CTCCCGAGCTCCTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" t="s">
+        <v>4570</v>
+      </c>
+      <c r="B244" t="s">
+        <v>4571</v>
+      </c>
+      <c r="C244" t="s">
+        <v>4572</v>
+      </c>
+      <c r="D244" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E244" t="str">
+        <f t="shared" si="1"/>
+        <v>TAGACTTCAGAGTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="s">
+        <v>4573</v>
+      </c>
+      <c r="B245" t="s">
+        <v>4574</v>
+      </c>
+      <c r="C245" t="s">
+        <v>4575</v>
+      </c>
+      <c r="D245" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E245" t="str">
+        <f t="shared" si="1"/>
+        <v>ACTTAGACTCTTTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" t="s">
+        <v>4576</v>
+      </c>
+      <c r="B246" t="s">
+        <v>4577</v>
+      </c>
+      <c r="C246" t="s">
+        <v>4578</v>
+      </c>
+      <c r="D246" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E246" t="str">
+        <f t="shared" si="1"/>
+        <v>GGACCTGGATGGTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" t="s">
+        <v>4579</v>
+      </c>
+      <c r="B247" t="s">
+        <v>4580</v>
+      </c>
+      <c r="C247" t="s">
+        <v>4581</v>
+      </c>
+      <c r="D247" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E247" t="str">
+        <f t="shared" si="1"/>
+        <v>TATGTGCCGGCTTCAGACTCCTTGGTCCGTGTTTCT</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F008B77-4F8B-4CF9-A2A1-E9CC06170AC2}">
   <dimension ref="A1:D141"/>
